--- a/docs/seep/files/xslope_johnson_res.xlsx
+++ b/docs/seep/files/xslope_johnson_res.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/seep/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0DE9744-E71D-1947-9344-17A4B25516E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147D5E9B-3F13-7A41-A659-2669FFF5EB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25160" yWindow="2540" windowWidth="34200" windowHeight="20240" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
@@ -1056,13 +1056,13 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1087,7 +1087,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="10">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -10284,37 +10305,37 @@
     <mergeCell ref="R7:V7"/>
   </mergeCells>
   <conditionalFormatting sqref="E9:F50">
-    <cfRule type="expression" dxfId="6" priority="4">
+    <cfRule type="expression" dxfId="9" priority="4">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:H50">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="8" priority="3">
       <formula>$D9="mc"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:J50">
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="7" priority="5">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M9:N50">
-    <cfRule type="expression" dxfId="3" priority="7">
+    <cfRule type="expression" dxfId="6" priority="7">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O9:O50">
-    <cfRule type="expression" dxfId="2" priority="14">
+    <cfRule type="expression" dxfId="5" priority="14">
       <formula>$D9="mc"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P9:Q50">
-    <cfRule type="expression" dxfId="1" priority="9">
+    <cfRule type="expression" dxfId="4" priority="9">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R9:V11">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10368,74 +10389,74 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="D4" s="45" t="s">
+      <c r="B4" s="47"/>
+      <c r="D4" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="45"/>
-      <c r="G4" s="45" t="s">
+      <c r="E4" s="47"/>
+      <c r="G4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="45"/>
-      <c r="J4" s="45" t="s">
+      <c r="H4" s="47"/>
+      <c r="J4" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="45"/>
-      <c r="M4" s="45" t="s">
+      <c r="K4" s="47"/>
+      <c r="M4" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="45"/>
-      <c r="P4" s="45" t="s">
+      <c r="N4" s="47"/>
+      <c r="P4" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="45"/>
+      <c r="Q4" s="47"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="45" t="s">
+      <c r="S4" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="45"/>
+      <c r="T4" s="47"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="45" t="s">
+      <c r="V4" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="45"/>
+      <c r="W4" s="47"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="45" t="s">
+      <c r="Y4" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="45"/>
+      <c r="Z4" s="47"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="45" t="s">
+      <c r="AB4" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="AC4" s="45"/>
-      <c r="AE4" s="45" t="s">
+      <c r="AC4" s="47"/>
+      <c r="AE4" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="AF4" s="45"/>
+      <c r="AF4" s="47"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="45" t="s">
+      <c r="AH4" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="AI4" s="45"/>
+      <c r="AI4" s="47"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="45" t="s">
+      <c r="AK4" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="AL4" s="45"/>
+      <c r="AL4" s="47"/>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="45" t="s">
+      <c r="AN4" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="AO4" s="45"/>
+      <c r="AO4" s="47"/>
       <c r="AP4" s="1"/>
-      <c r="AQ4" s="45" t="s">
+      <c r="AQ4" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="AR4" s="45"/>
+      <c r="AR4" s="47"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="41" t="s">
@@ -10538,89 +10559,89 @@
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="46" t="str">
+      <c r="A6" s="45" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>shell</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="D6" s="46" t="str">
+      <c r="B6" s="46"/>
+      <c r="D6" s="45" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>core</v>
       </c>
-      <c r="E6" s="47"/>
-      <c r="G6" s="46" t="str">
+      <c r="E6" s="46"/>
+      <c r="G6" s="45" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>foundation</v>
       </c>
-      <c r="H6" s="47"/>
-      <c r="J6" s="46" t="str">
+      <c r="H6" s="46"/>
+      <c r="J6" s="45" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="47"/>
-      <c r="M6" s="46" t="str">
+      <c r="K6" s="46"/>
+      <c r="M6" s="45" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="47"/>
-      <c r="P6" s="46" t="str">
+      <c r="N6" s="46"/>
+      <c r="P6" s="45" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="47"/>
+      <c r="Q6" s="46"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="46" t="str">
+      <c r="S6" s="45" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="47"/>
+      <c r="T6" s="46"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="46" t="str">
+      <c r="V6" s="45" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="47"/>
+      <c r="W6" s="46"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="46" t="str">
+      <c r="Y6" s="45" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="47"/>
+      <c r="Z6" s="46"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="46" t="str">
+      <c r="AB6" s="45" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="47"/>
-      <c r="AE6" s="46" t="str">
+      <c r="AC6" s="46"/>
+      <c r="AE6" s="45" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="47"/>
+      <c r="AF6" s="46"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="46" t="str">
+      <c r="AH6" s="45" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="47"/>
+      <c r="AI6" s="46"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="46" t="str">
+      <c r="AK6" s="45" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="47"/>
+      <c r="AL6" s="46"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="46" t="str">
+      <c r="AN6" s="45" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="47"/>
+      <c r="AO6" s="46"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="46" t="str">
+      <c r="AQ6" s="45" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="47"/>
+      <c r="AR6" s="46"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -11584,36 +11605,36 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
     <mergeCell ref="AE6:AF6"/>
     <mergeCell ref="AH6:AI6"/>
     <mergeCell ref="AK6:AL6"/>
     <mergeCell ref="AN6:AO6"/>
     <mergeCell ref="AQ6:AR6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11971,12 +11992,24 @@
       <c r="N16" s="1"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D12" xr:uid="{06E9E004-FC39-FE49-926A-912F810F5089}">
+  <conditionalFormatting sqref="E3:E42">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>OR($D3="Intercept", $D3="Radius")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:G42">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>OR($D3="Depth",$D3="Radius")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H42">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>OR($D3="Depth",$D3="Intercept")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D52" xr:uid="{EE74CB11-F5EC-2644-90FF-E9396C6F334C}">
       <formula1>$J$3:$J$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D4" xr:uid="{AEFC92A9-AB07-FF4B-9461-938B9BDCD07D}">
-      <formula1>$J$5:$J$7</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/seep/files/xslope_johnson_res.xlsx
+++ b/docs/seep/files/xslope_johnson_res.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/seep/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147D5E9B-3F13-7A41-A659-2669FFF5EB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7FCB456-66D8-CC4C-A571-5A6105E1A4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25160" yWindow="2540" windowWidth="34200" windowHeight="20240" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="36900" yWindow="4240" windowWidth="30840" windowHeight="19760" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="156">
   <si>
     <t>X</t>
   </si>
@@ -1056,13 +1056,13 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2524,6 +2524,15 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>320</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -2533,6 +2542,15 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>160</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -9573,15 +9591,25 @@
       <c r="B9" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+      <c r="C9" s="3">
+        <v>130</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="3">
+        <v>100</v>
+      </c>
+      <c r="F9" s="3">
+        <v>35</v>
+      </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="K9" s="3" t="s">
+        <v>91</v>
+      </c>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
@@ -9603,8 +9631,12 @@
       <c r="V9" s="3">
         <v>-1</v>
       </c>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
+      <c r="W9" s="3">
+        <v>200000</v>
+      </c>
+      <c r="X9" s="3">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
@@ -9613,15 +9645,25 @@
       <c r="B10" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="C10" s="3">
+        <v>125</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="3">
+        <v>400</v>
+      </c>
+      <c r="F10" s="3">
+        <v>18</v>
+      </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="K10" s="3" t="s">
+        <v>91</v>
+      </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
@@ -9643,8 +9685,12 @@
       <c r="V10" s="3">
         <v>-1</v>
       </c>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
+      <c r="W10" s="3">
+        <v>30000</v>
+      </c>
+      <c r="X10" s="3">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
@@ -9653,15 +9699,25 @@
       <c r="B11" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="C11" s="3">
+        <v>127</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="3">
+        <v>100</v>
+      </c>
+      <c r="F11" s="3">
+        <v>27</v>
+      </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="K11" s="3" t="s">
+        <v>91</v>
+      </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
@@ -9683,8 +9739,12 @@
       <c r="V11" s="3">
         <v>-1</v>
       </c>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
+      <c r="W11" s="3">
+        <v>50000</v>
+      </c>
+      <c r="X11" s="3">
+        <v>0.35</v>
+      </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
@@ -10389,74 +10449,74 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="D4" s="47" t="s">
+      <c r="B4" s="45"/>
+      <c r="D4" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="47"/>
-      <c r="G4" s="47" t="s">
+      <c r="E4" s="45"/>
+      <c r="G4" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="47"/>
-      <c r="J4" s="47" t="s">
+      <c r="H4" s="45"/>
+      <c r="J4" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="47"/>
-      <c r="M4" s="47" t="s">
+      <c r="K4" s="45"/>
+      <c r="M4" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="47"/>
-      <c r="P4" s="47" t="s">
+      <c r="N4" s="45"/>
+      <c r="P4" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="47"/>
+      <c r="Q4" s="45"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="47" t="s">
+      <c r="S4" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="47"/>
+      <c r="T4" s="45"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="47" t="s">
+      <c r="V4" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="47"/>
+      <c r="W4" s="45"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="47" t="s">
+      <c r="Y4" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="47"/>
+      <c r="Z4" s="45"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="47" t="s">
+      <c r="AB4" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="AC4" s="47"/>
-      <c r="AE4" s="47" t="s">
+      <c r="AC4" s="45"/>
+      <c r="AE4" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="AF4" s="47"/>
+      <c r="AF4" s="45"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="47" t="s">
+      <c r="AH4" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="AI4" s="47"/>
+      <c r="AI4" s="45"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="47" t="s">
+      <c r="AK4" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="AL4" s="47"/>
+      <c r="AL4" s="45"/>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="47" t="s">
+      <c r="AN4" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="AO4" s="47"/>
+      <c r="AO4" s="45"/>
       <c r="AP4" s="1"/>
-      <c r="AQ4" s="47" t="s">
+      <c r="AQ4" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="AR4" s="47"/>
+      <c r="AR4" s="45"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="41" t="s">
@@ -10559,89 +10619,89 @@
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="45" t="str">
+      <c r="A6" s="46" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>shell</v>
       </c>
-      <c r="B6" s="46"/>
-      <c r="D6" s="45" t="str">
+      <c r="B6" s="47"/>
+      <c r="D6" s="46" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>core</v>
       </c>
-      <c r="E6" s="46"/>
-      <c r="G6" s="45" t="str">
+      <c r="E6" s="47"/>
+      <c r="G6" s="46" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>foundation</v>
       </c>
-      <c r="H6" s="46"/>
-      <c r="J6" s="45" t="str">
+      <c r="H6" s="47"/>
+      <c r="J6" s="46" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="46"/>
-      <c r="M6" s="45" t="str">
+      <c r="K6" s="47"/>
+      <c r="M6" s="46" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="46"/>
-      <c r="P6" s="45" t="str">
+      <c r="N6" s="47"/>
+      <c r="P6" s="46" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="46"/>
+      <c r="Q6" s="47"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="45" t="str">
+      <c r="S6" s="46" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="46"/>
+      <c r="T6" s="47"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="45" t="str">
+      <c r="V6" s="46" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="46"/>
+      <c r="W6" s="47"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="45" t="str">
+      <c r="Y6" s="46" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="46"/>
+      <c r="Z6" s="47"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="45" t="str">
+      <c r="AB6" s="46" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="46"/>
-      <c r="AE6" s="45" t="str">
+      <c r="AC6" s="47"/>
+      <c r="AE6" s="46" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="46"/>
+      <c r="AF6" s="47"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="45" t="str">
+      <c r="AH6" s="46" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="46"/>
+      <c r="AI6" s="47"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="45" t="str">
+      <c r="AK6" s="46" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="46"/>
+      <c r="AL6" s="47"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="45" t="str">
+      <c r="AN6" s="46" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="46"/>
+      <c r="AO6" s="47"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="45" t="str">
+      <c r="AQ6" s="46" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="46"/>
+      <c r="AR6" s="47"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -11605,36 +11665,36 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AK6:AL6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AK6:AL6"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AQ6:AR6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11851,10 +11911,18 @@
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="B3" s="3">
+        <v>500</v>
+      </c>
+      <c r="C3" s="3">
+        <v>200</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="3">
+        <v>60</v>
+      </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -11869,10 +11937,18 @@
       <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="B4" s="3">
+        <v>240</v>
+      </c>
+      <c r="C4" s="3">
+        <v>200</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="3">
+        <v>60</v>
+      </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -12284,9 +12360,16 @@
       </c>
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>100</v>
+      </c>
+      <c r="D4" s="3">
+        <f>60*62.4</f>
+        <v>3744</v>
+      </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -12304,9 +12387,16 @@
       <c r="X4" s="3"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="B5" s="3">
+        <v>200</v>
+      </c>
+      <c r="C5" s="3">
+        <v>100</v>
+      </c>
+      <c r="D5" s="3">
+        <f>D4</f>
+        <v>3744</v>
+      </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -12324,9 +12414,15 @@
       <c r="X5" s="3"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="B6" s="3">
+        <v>320</v>
+      </c>
+      <c r="C6" s="3">
+        <v>160</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>

--- a/docs/seep/files/xslope_johnson_res.xlsx
+++ b/docs/seep/files/xslope_johnson_res.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/seep/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7FCB456-66D8-CC4C-A571-5A6105E1A4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7DD7711-AC8D-4E44-8A07-B9B842E5B1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36900" yWindow="4240" windowWidth="30840" windowHeight="19760" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="36900" yWindow="4240" windowWidth="30840" windowHeight="19760" activeTab="5" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="156">
   <si>
     <t>X</t>
   </si>
@@ -11921,7 +11921,7 @@
         <v>26</v>
       </c>
       <c r="E3" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -11937,18 +11937,10 @@
       <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="3">
-        <v>240</v>
-      </c>
-      <c r="C4" s="3">
-        <v>200</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="3">
-        <v>60</v>
-      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>

--- a/docs/seep/files/xslope_johnson_res.xlsx
+++ b/docs/seep/files/xslope_johnson_res.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
   <si>
     <t>X</t>
   </si>
@@ -630,6 +630,37 @@
   </si>
   <si>
     <t>foundation</t>
+  </si>
+  <si>
+    <t>psi</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>psi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -8064,7 +8095,7 @@
         <v>79</v>
       </c>
       <c r="D5" s="35">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -9538,8 +9569,8 @@
       <c r="I8" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="J8" s="26" t="s">
-        <v>81</v>
+      <c r="J8" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="K8" s="21" t="s">
         <v>88</v>
@@ -9560,7 +9591,7 @@
         <v>82</v>
       </c>
       <c r="Q8" s="23" t="s">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="R8" s="25" t="s">
         <v>92</v>
@@ -10364,7 +10395,7 @@
     <mergeCell ref="W7:X7"/>
     <mergeCell ref="R7:V7"/>
   </mergeCells>
-  <conditionalFormatting sqref="E9:F50">
+  <conditionalFormatting sqref="F9:F50">
     <cfRule type="expression" dxfId="9" priority="4">
       <formula>$D9="cp"</formula>
     </cfRule>
@@ -10379,7 +10410,7 @@
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M9:N50">
+  <conditionalFormatting sqref="N9:N50">
     <cfRule type="expression" dxfId="6" priority="7">
       <formula>$D9="cp"</formula>
     </cfRule>

--- a/docs/seep/files/xslope_johnson_res.xlsx
+++ b/docs/seep/files/xslope_johnson_res.xlsx
@@ -679,13 +679,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0432FF"/>
-        <bgColor rgb="FF0071BF"/>
+        <bgColor rgb="FF0072BD"/>
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="darkGray">
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="-0.25"/>
-        <bgColor rgb="FF3E8625"/>
+        <bgColor rgb="FF1C691F"/>
       </patternFill>
     </fill>
     <fill>
@@ -708,7 +708,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0071BF"/>
+        <fgColor rgb="FF0072BD"/>
         <bgColor rgb="FF0C6486"/>
       </patternFill>
     </fill>
@@ -745,7 +745,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor rgb="FF3E8625"/>
+        <bgColor rgb="FF3A8022"/>
       </patternFill>
     </fill>
     <fill>
@@ -824,8 +824,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -833,11 +837,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -853,7 +857,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -861,7 +865,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -957,11 +961,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1078,10 +1082,10 @@
       <rgbColor rgb="FFC00000"/>
       <rgbColor rgb="FF1C691F"/>
       <rgbColor rgb="FF155218"/>
-      <rgbColor rgb="FF3E8625"/>
+      <rgbColor rgb="FF3A8022"/>
       <rgbColor rgb="FF78206E"/>
       <rgbColor rgb="FF0C6486"/>
-      <rgbColor rgb="FFA3B2A3"/>
+      <rgbColor rgb="FFA1DF8B"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF64BEE6"/>
       <rgbColor rgb="FFA02B93"/>
@@ -1089,25 +1093,25 @@
       <rgbColor rgb="FFCAEEFB"/>
       <rgbColor rgb="FF601A58"/>
       <rgbColor rgb="FFED8D5B"/>
-      <rgbColor rgb="FF0071BF"/>
-      <rgbColor rgb="FF8ED973"/>
-      <rgbColor rgb="FF3A7C22"/>
+      <rgbColor rgb="FF0072BD"/>
+      <rgbColor rgb="FFD3D3D3"/>
+      <rgbColor rgb="FF595959"/>
       <rgbColor rgb="FFD156C4"/>
       <rgbColor rgb="FFC04F15"/>
       <rgbColor rgb="FF66DB76"/>
       <rgbColor rgb="FF701E67"/>
       <rgbColor rgb="FF80350E"/>
-      <rgbColor rgb="FF139CD7"/>
+      <rgbColor rgb="FF1199D1"/>
       <rgbColor rgb="FFB34A13"/>
-      <rgbColor rgb="FF46B1E1"/>
+      <rgbColor rgb="FF27A3DC"/>
       <rgbColor rgb="FFE8E8E8"/>
-      <rgbColor rgb="FFA1DF8B"/>
+      <rgbColor rgb="FF8ED973"/>
       <rgbColor rgb="FFD86ECC"/>
       <rgbColor rgb="FF7BD4F6"/>
       <rgbColor rgb="FFF2AA84"/>
       <rgbColor rgb="FFDE86D5"/>
       <rgbColor rgb="FFF4B898"/>
-      <rgbColor rgb="FF595959"/>
+      <rgbColor rgb="FF46B1E1"/>
       <rgbColor rgb="FF35BFF2"/>
       <rgbColor rgb="FF7BD25C"/>
       <rgbColor rgb="FF68CC45"/>
@@ -6640,7 +6644,7 @@
               <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="a2b2a2"/>
+                  <a:srgbClr val="27a3dc"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
@@ -6652,7 +6656,7 @@
               <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="a2b2a2"/>
+                  <a:srgbClr val="27a3dc"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
@@ -6664,7 +6668,7 @@
               <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="a2b2a2"/>
+                  <a:srgbClr val="27a3dc"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
@@ -6676,7 +6680,7 @@
               <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="a2b2a2"/>
+                  <a:srgbClr val="27a3dc"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
@@ -6688,7 +6692,7 @@
               <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="a2b2a2"/>
+                  <a:srgbClr val="27a3dc"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
@@ -6700,7 +6704,7 @@
               <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="a2b2a2"/>
+                  <a:srgbClr val="27a3dc"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
@@ -6712,7 +6716,7 @@
               <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="a2b2a2"/>
+                  <a:srgbClr val="27a3dc"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
@@ -6724,7 +6728,7 @@
               <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="a2b2a2"/>
+                  <a:srgbClr val="27a3dc"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
@@ -6736,7 +6740,7 @@
               <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="a2b2a2"/>
+                  <a:srgbClr val="27a3dc"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
@@ -6748,7 +6752,7 @@
               <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="a2b2a2"/>
+                  <a:srgbClr val="27a3dc"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
@@ -6760,7 +6764,7 @@
               <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="a2b2a2"/>
+                  <a:srgbClr val="27a3dc"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
@@ -6772,7 +6776,7 @@
               <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="a2b2a2"/>
+                  <a:srgbClr val="27a3dc"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
@@ -6784,7 +6788,7 @@
               <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="a2b2a2"/>
+                  <a:srgbClr val="27a3dc"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
@@ -6796,7 +6800,7 @@
               <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="a2b2a2"/>
+                  <a:srgbClr val="27a3dc"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
@@ -6808,7 +6812,7 @@
               <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="a2b2a2"/>
+                  <a:srgbClr val="27a3dc"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
@@ -6820,7 +6824,7 @@
               <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="a2b2a2"/>
+                  <a:srgbClr val="27a3dc"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
@@ -6832,7 +6836,7 @@
               <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="a2b2a2"/>
+                  <a:srgbClr val="27a3dc"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
@@ -6844,7 +6848,7 @@
               <c:size val="5"/>
               <c:spPr>
                 <a:solidFill>
-                  <a:srgbClr val="a2b2a2"/>
+                  <a:srgbClr val="27a3dc"/>
                 </a:solidFill>
               </c:spPr>
             </c:marker>
@@ -8423,11 +8427,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="19879542"/>
-        <c:axId val="21746847"/>
+        <c:axId val="35654039"/>
+        <c:axId val="79549709"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="19879542"/>
+        <c:axId val="35654039"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8470,12 +8474,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21746847"/>
+        <c:crossAx val="79549709"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="21746847"/>
+        <c:axId val="79549709"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8518,7 +8522,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19879542"/>
+        <c:crossAx val="35654039"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -8582,9 +8586,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>609120</xdr:colOff>
+      <xdr:colOff>608760</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>141840</xdr:rowOff>
+      <xdr:rowOff>141480</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -8593,7 +8597,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="589680" y="390600"/>
-        <a:ext cx="10287360" cy="6752160"/>
+        <a:ext cx="10287000" cy="6751800"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -8786,163 +8790,163 @@
   <dimension ref="A1:G24"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="52.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="2" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="52.82"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C5" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="2" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="F7" s="6" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="F7" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="2" t="n">
         <v>62.4</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="4" t="s">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="4" t="s">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="0" t="s">
+      <c r="G10" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1"/>
-      <c r="C11" s="4" t="s">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="2"/>
+      <c r="C11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="0" t="s">
+      <c r="G11" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F12" s="1" t="s">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="0" t="s">
+      <c r="G12" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F13" s="1" t="s">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G13" s="0" t="s">
+      <c r="G13" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F14" s="1" t="s">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="0" t="s">
+      <c r="G14" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F15" s="1" t="s">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="0" t="s">
+      <c r="G15" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F16" s="1" t="s">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G16" s="0" t="s">
+      <c r="G16" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="1"/>
-      <c r="F17" s="1" t="s">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="2"/>
+      <c r="F17" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F18" s="1" t="s">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="1"/>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="1"/>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8966,360 +8970,360 @@
   <dimension ref="A2:N25"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="1" width="10.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="4.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="2" width="10.82"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="38" t="s">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="39" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="E2" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="F2" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="G2" s="42" t="s">
+      <c r="G2" s="43" t="s">
         <v>137</v>
       </c>
-      <c r="H2" s="41" t="s">
+      <c r="H2" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="41" t="s">
+      <c r="I2" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="J2" s="42" t="s">
+      <c r="J2" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="K2" s="42" t="s">
+      <c r="K2" s="43" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="n">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-    </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="n">
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-    </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="n">
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="n">
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="n">
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="n">
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="n">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="n">
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="n">
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="n">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="n">
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="n">
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="n">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="n">
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="n">
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="n">
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="n">
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="M19" s="43"/>
-      <c r="N19" s="8" t="s">
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="9" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="n">
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="8" t="s">
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="M20" s="45"/>
+      <c r="N20" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="n">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="n">
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-    </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+    </row>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -9340,413 +9344,413 @@
   <dimension ref="B2:R24"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="4.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="4.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="4"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="45" t="s">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="E2" s="31" t="s">
+      <c r="C2" s="46"/>
+      <c r="E2" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="F2" s="31"/>
-      <c r="H2" s="31" t="s">
+      <c r="F2" s="32"/>
+      <c r="H2" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="I2" s="31"/>
-      <c r="K2" s="31" t="s">
+      <c r="I2" s="32"/>
+      <c r="K2" s="32" t="s">
         <v>146</v>
       </c>
-      <c r="L2" s="31"/>
-      <c r="N2" s="31" t="s">
+      <c r="L2" s="32"/>
+      <c r="N2" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="O2" s="31"/>
-      <c r="Q2" s="31" t="s">
+      <c r="O2" s="32"/>
+      <c r="Q2" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="R2" s="31"/>
-    </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="E3" s="46" t="s">
+      <c r="R2" s="32"/>
+    </row>
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="E3" s="47" t="s">
         <v>149</v>
       </c>
-      <c r="F3" s="47" t="n">
+      <c r="F3" s="48" t="n">
         <v>160</v>
       </c>
-      <c r="H3" s="46" t="s">
+      <c r="H3" s="47" t="s">
         <v>149</v>
       </c>
-      <c r="I3" s="47" t="n">
+      <c r="I3" s="48" t="n">
         <v>100</v>
       </c>
-      <c r="K3" s="46" t="s">
+      <c r="K3" s="47" t="s">
         <v>149</v>
       </c>
-      <c r="L3" s="47"/>
-      <c r="N3" s="46" t="s">
+      <c r="L3" s="48"/>
+      <c r="N3" s="47" t="s">
         <v>149</v>
       </c>
-      <c r="O3" s="47"/>
-      <c r="Q3" s="46" t="s">
+      <c r="O3" s="48"/>
+      <c r="Q3" s="47" t="s">
         <v>149</v>
       </c>
-      <c r="R3" s="47"/>
-    </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="48" t="s">
+      <c r="R3" s="48"/>
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="C4" s="48" t="s">
+      <c r="C4" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="E4" s="48" t="s">
+      <c r="E4" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="F4" s="48" t="s">
+      <c r="F4" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="H4" s="48" t="s">
+      <c r="H4" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="I4" s="48" t="s">
+      <c r="I4" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="K4" s="48" t="s">
+      <c r="K4" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="L4" s="48" t="s">
+      <c r="L4" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="N4" s="48" t="s">
+      <c r="N4" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="O4" s="48" t="s">
+      <c r="O4" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="Q4" s="48" t="s">
+      <c r="Q4" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="R4" s="48" t="s">
+      <c r="R4" s="49" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="19" t="n">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="20" t="n">
         <v>380</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="20" t="n">
         <v>180</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="H5" s="19" t="n">
+      <c r="H5" s="20" t="n">
         <v>550</v>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="I5" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="19"/>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="19" t="n">
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="20" t="n">
         <v>550</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="20" t="n">
         <v>200</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="H6" s="19" t="n">
+      <c r="H6" s="20" t="n">
         <v>750</v>
       </c>
-      <c r="I6" s="19" t="n">
+      <c r="I6" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="19"/>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="E7" s="19" t="n">
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="E7" s="20" t="n">
         <v>320</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="20" t="n">
         <v>160</v>
       </c>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="Q7" s="19"/>
-      <c r="R7" s="19"/>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="19"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="19"/>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="19"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="19"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="Q14" s="19"/>
-      <c r="R14" s="19"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="Q15" s="19"/>
-      <c r="R15" s="19"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="19"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="19"/>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="19"/>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="19"/>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="19"/>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20"/>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="20"/>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="20"/>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="20"/>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="Q21" s="20"/>
+      <c r="R21" s="20"/>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="Q22" s="20"/>
+      <c r="R22" s="20"/>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="20"/>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -9775,381 +9779,381 @@
   <dimension ref="B2:R24"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="4.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="4.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="4"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="49" t="s">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="50" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="E2" s="32" t="s">
+      <c r="C2" s="50"/>
+      <c r="E2" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="F2" s="32"/>
-      <c r="H2" s="32" t="s">
+      <c r="F2" s="33"/>
+      <c r="H2" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="I2" s="32"/>
-      <c r="K2" s="32" t="s">
+      <c r="I2" s="33"/>
+      <c r="K2" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="L2" s="32"/>
-      <c r="N2" s="32" t="s">
+      <c r="L2" s="33"/>
+      <c r="N2" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="O2" s="32"/>
-      <c r="Q2" s="32" t="s">
+      <c r="O2" s="33"/>
+      <c r="Q2" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="R2" s="32"/>
-    </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="E3" s="50" t="s">
+      <c r="R2" s="33"/>
+    </row>
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="E3" s="51" t="s">
         <v>149</v>
       </c>
-      <c r="F3" s="51"/>
-      <c r="H3" s="50" t="s">
+      <c r="F3" s="52"/>
+      <c r="H3" s="51" t="s">
         <v>149</v>
       </c>
-      <c r="I3" s="51"/>
-      <c r="K3" s="50" t="s">
+      <c r="I3" s="52"/>
+      <c r="K3" s="51" t="s">
         <v>149</v>
       </c>
-      <c r="L3" s="51"/>
-      <c r="N3" s="50" t="s">
+      <c r="L3" s="52"/>
+      <c r="N3" s="51" t="s">
         <v>149</v>
       </c>
-      <c r="O3" s="51"/>
-      <c r="Q3" s="50" t="s">
+      <c r="O3" s="52"/>
+      <c r="Q3" s="51" t="s">
         <v>149</v>
       </c>
-      <c r="R3" s="51"/>
-    </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="48" t="s">
+      <c r="R3" s="52"/>
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="C4" s="48" t="s">
+      <c r="C4" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="E4" s="48" t="s">
+      <c r="E4" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="F4" s="48" t="s">
+      <c r="F4" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="H4" s="48" t="s">
+      <c r="H4" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="I4" s="48" t="s">
+      <c r="I4" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="K4" s="48" t="s">
+      <c r="K4" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="L4" s="48" t="s">
+      <c r="L4" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="N4" s="48" t="s">
+      <c r="N4" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="O4" s="48" t="s">
+      <c r="O4" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="Q4" s="48" t="s">
+      <c r="Q4" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="R4" s="48" t="s">
+      <c r="R4" s="49" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="19"/>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="19"/>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="Q7" s="19"/>
-      <c r="R7" s="19"/>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="19"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="19"/>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="19"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="19"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="Q14" s="19"/>
-      <c r="R14" s="19"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="Q15" s="19"/>
-      <c r="R15" s="19"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="19"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="19"/>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="19"/>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="19"/>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="19"/>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20"/>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="20"/>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="20"/>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="20"/>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="Q21" s="20"/>
+      <c r="R21" s="20"/>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="Q22" s="20"/>
+      <c r="R22" s="20"/>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="20"/>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -10197,946 +10201,946 @@
   <dimension ref="A2:X50"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="1" width="8.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="10" style="0" width="8.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="14" style="0" width="10.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="10.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="17.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="2" width="8.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="10" style="1" width="8.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="14" style="1" width="10.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="2" width="10.82"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C2" s="9" t="s">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C2" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="9"/>
-    </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="1" t="s">
+      <c r="O2" s="10"/>
+    </row>
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K3" s="0" t="s">
+      <c r="K3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="O3" s="4"/>
-    </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="1" t="s">
+      <c r="O3" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="0" t="s">
+      <c r="K4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J5" s="1" t="s">
+      <c r="O4" s="5"/>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="O5" s="4"/>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="10" t="s">
+      <c r="O5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C7" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="10" t="s">
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10" t="s">
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10"/>
-      <c r="U7" s="10"/>
-      <c r="V7" s="10"/>
-      <c r="W7" s="10" t="s">
+      <c r="S7" s="11"/>
+      <c r="T7" s="11"/>
+      <c r="U7" s="11"/>
+      <c r="V7" s="11"/>
+      <c r="W7" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="X7" s="10"/>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
+      <c r="X7" s="11"/>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="H8" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="K8" s="13" t="s">
+      <c r="K8" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="14" t="s">
+      <c r="L8" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M8" s="14" t="s">
+      <c r="M8" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="N8" s="15" t="s">
+      <c r="N8" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="O8" s="14" t="s">
+      <c r="O8" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="P8" s="14" t="s">
+      <c r="P8" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="Q8" s="15" t="s">
+      <c r="Q8" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="R8" s="16" t="s">
+      <c r="R8" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="S8" s="16" t="s">
+      <c r="S8" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="T8" s="16" t="s">
+      <c r="T8" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="U8" s="16" t="s">
+      <c r="U8" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="V8" s="16" t="s">
+      <c r="V8" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="W8" s="17" t="s">
+      <c r="W8" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="X8" s="18" t="s">
+      <c r="X8" s="19" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="n">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="20" t="n">
         <v>130</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="20" t="n">
         <v>35</v>
       </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="20" t="s">
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19" t="n">
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="S9" s="19" t="n">
+      <c r="S9" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="19" t="n">
+      <c r="T9" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="U9" s="19" t="n">
+      <c r="U9" s="20" t="n">
         <v>0.01</v>
       </c>
-      <c r="V9" s="19" t="n">
+      <c r="V9" s="20" t="n">
         <v>-1</v>
       </c>
-      <c r="W9" s="19" t="n">
+      <c r="W9" s="20" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="X9" s="20" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>125</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>400</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="S10" s="20" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="T10" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V10" s="20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W10" s="20" t="n">
         <v>200000</v>
       </c>
-      <c r="X9" s="19" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="19" t="n">
-        <v>125</v>
-      </c>
-      <c r="D10" s="20" t="s">
+      <c r="X10" s="20" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="20" t="n">
+        <v>127</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="19" t="n">
-        <v>400</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>18</v>
-      </c>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="20" t="s">
+      <c r="E11" s="20" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" s="20" t="n">
+        <v>27</v>
+      </c>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="19" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="S10" s="19" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="T10" s="19" t="n">
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S11" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T11" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="U10" s="19" t="n">
+      <c r="U11" s="20" t="n">
         <v>0.01</v>
       </c>
-      <c r="V10" s="19" t="n">
+      <c r="V11" s="20" t="n">
         <v>-1</v>
       </c>
-      <c r="W10" s="19" t="n">
-        <v>150000</v>
-      </c>
-      <c r="X10" s="19" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="19" t="n">
-        <v>127</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>100</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>27</v>
-      </c>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="S11" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="19" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V11" s="19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W11" s="19" t="n">
-        <v>50000</v>
-      </c>
-      <c r="X11" s="19" t="n">
+      <c r="W11" s="20" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="X11" s="20" t="n">
         <v>0.35</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="n">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="19"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="19"/>
-      <c r="U12" s="19"/>
-      <c r="V12" s="19"/>
-      <c r="W12" s="19"/>
-      <c r="X12" s="19"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="n">
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="20"/>
+      <c r="U12" s="20"/>
+      <c r="V12" s="20"/>
+      <c r="W12" s="20"/>
+      <c r="X12" s="20"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="19"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="19"/>
-      <c r="U13" s="19"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="19"/>
-      <c r="X13" s="19"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="n">
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="20"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="20"/>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="19"/>
-      <c r="R14" s="19"/>
-      <c r="S14" s="19"/>
-      <c r="T14" s="19"/>
-      <c r="U14" s="19"/>
-      <c r="V14" s="19"/>
-      <c r="W14" s="19"/>
-      <c r="X14" s="19"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="n">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="20"/>
+      <c r="T14" s="20"/>
+      <c r="U14" s="20"/>
+      <c r="V14" s="20"/>
+      <c r="W14" s="20"/>
+      <c r="X14" s="20"/>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="P15" s="19"/>
-      <c r="Q15" s="19"/>
-      <c r="R15" s="19"/>
-      <c r="S15" s="19"/>
-      <c r="T15" s="19"/>
-      <c r="U15" s="19"/>
-      <c r="V15" s="19"/>
-      <c r="W15" s="19"/>
-      <c r="X15" s="19"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="n">
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="20"/>
+      <c r="V15" s="20"/>
+      <c r="W15" s="20"/>
+      <c r="X15" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="19"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
-      <c r="U16" s="19"/>
-      <c r="V16" s="19"/>
-      <c r="W16" s="19"/>
-      <c r="X16" s="19"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="n">
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="20"/>
+      <c r="V16" s="20"/>
+      <c r="W16" s="20"/>
+      <c r="X16" s="20"/>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
-      <c r="S17" s="19"/>
-      <c r="T17" s="19"/>
-      <c r="U17" s="19"/>
-      <c r="V17" s="19"/>
-      <c r="W17" s="19"/>
-      <c r="X17" s="19"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="n">
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="20"/>
+      <c r="V17" s="20"/>
+      <c r="W17" s="20"/>
+      <c r="X17" s="20"/>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-      <c r="U18" s="19"/>
-      <c r="V18" s="19"/>
-      <c r="W18" s="19"/>
-      <c r="X18" s="19"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="n">
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="20"/>
+      <c r="S18" s="20"/>
+      <c r="T18" s="20"/>
+      <c r="U18" s="20"/>
+      <c r="V18" s="20"/>
+      <c r="W18" s="20"/>
+      <c r="X18" s="20"/>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="19"/>
-      <c r="S19" s="19"/>
-      <c r="T19" s="19"/>
-      <c r="U19" s="19"/>
-      <c r="V19" s="19"/>
-      <c r="W19" s="19"/>
-      <c r="X19" s="19"/>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="n">
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="20"/>
+      <c r="T19" s="20"/>
+      <c r="U19" s="20"/>
+      <c r="V19" s="20"/>
+      <c r="W19" s="20"/>
+      <c r="X19" s="20"/>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="19"/>
-      <c r="S20" s="19"/>
-      <c r="T20" s="19"/>
-      <c r="U20" s="19"/>
-      <c r="V20" s="19"/>
-      <c r="W20" s="19"/>
-      <c r="X20" s="19"/>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="n">
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="20"/>
+      <c r="T20" s="20"/>
+      <c r="U20" s="20"/>
+      <c r="V20" s="20"/>
+      <c r="W20" s="20"/>
+      <c r="X20" s="20"/>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
-      <c r="S21" s="19"/>
-      <c r="T21" s="19"/>
-      <c r="U21" s="19"/>
-      <c r="V21" s="19"/>
-      <c r="W21" s="19"/>
-      <c r="X21" s="19"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="n">
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="20"/>
+      <c r="T21" s="20"/>
+      <c r="U21" s="20"/>
+      <c r="V21" s="20"/>
+      <c r="W21" s="20"/>
+      <c r="X21" s="20"/>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="19"/>
-      <c r="S22" s="19"/>
-      <c r="T22" s="19"/>
-      <c r="U22" s="19"/>
-      <c r="V22" s="19"/>
-      <c r="W22" s="19"/>
-      <c r="X22" s="19"/>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="n">
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
+      <c r="R22" s="20"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="20"/>
+      <c r="U22" s="20"/>
+      <c r="V22" s="20"/>
+      <c r="W22" s="20"/>
+      <c r="X22" s="20"/>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="19"/>
-      <c r="S23" s="19"/>
-      <c r="T23" s="19"/>
-      <c r="U23" s="19"/>
-      <c r="V23" s="19"/>
-      <c r="W23" s="19"/>
-      <c r="X23" s="19"/>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-    </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-    </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
-    </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-    </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-    </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-    </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-    </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-    </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-    </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-    </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
-    </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
-    </row>
-    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
-    </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
-    </row>
-    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
-    </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
-    </row>
-    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-      <c r="P40" s="1"/>
-      <c r="Q40" s="1"/>
-    </row>
-    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
-      <c r="Q41" s="1"/>
-    </row>
-    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
-    </row>
-    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
-    </row>
-    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
-    </row>
-    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-      <c r="P45" s="1"/>
-      <c r="Q45" s="1"/>
-    </row>
-    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="1"/>
-      <c r="Q46" s="1"/>
-    </row>
-    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1"/>
-      <c r="Q47" s="1"/>
-    </row>
-    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1"/>
-      <c r="Q48" s="1"/>
-    </row>
-    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-      <c r="N49" s="1"/>
-      <c r="O49" s="1"/>
-      <c r="P49" s="1"/>
-      <c r="Q49" s="1"/>
-    </row>
-    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
-      <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
-      <c r="P50" s="1"/>
-      <c r="Q50" s="1"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="20"/>
+      <c r="V23" s="20"/>
+      <c r="W23" s="20"/>
+      <c r="X23" s="20"/>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+    </row>
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+    </row>
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+    </row>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+    </row>
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+    </row>
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
+    </row>
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
+    </row>
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2"/>
+    </row>
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="2"/>
+    </row>
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
+    </row>
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
+    </row>
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" s="2"/>
+      <c r="Q49" s="2"/>
+    </row>
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" s="2"/>
+      <c r="Q50" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -11208,1252 +11212,1252 @@
   <dimension ref="A2:AR27"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="10.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="10.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="10.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="10.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="0" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="0" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="2" width="10.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="2" width="10.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="2" width="10.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="2" width="10.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="2" width="10.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="1" width="3.83"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="19" t="n">
+      <c r="B2" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="23" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="s">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="D4" s="23" t="s">
+      <c r="B4" s="24"/>
+      <c r="D4" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="23"/>
-      <c r="G4" s="23" t="s">
+      <c r="E4" s="24"/>
+      <c r="G4" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="H4" s="23"/>
-      <c r="J4" s="23" t="s">
+      <c r="H4" s="24"/>
+      <c r="J4" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="23"/>
-      <c r="M4" s="23" t="s">
+      <c r="K4" s="24"/>
+      <c r="M4" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="N4" s="23"/>
-      <c r="P4" s="23" t="s">
+      <c r="N4" s="24"/>
+      <c r="P4" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="Q4" s="23"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="23" t="s">
+      <c r="Q4" s="24"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="T4" s="23"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="23" t="s">
+      <c r="T4" s="24"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="W4" s="23"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="23" t="s">
+      <c r="W4" s="24"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="Z4" s="23"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="23" t="s">
+      <c r="Z4" s="24"/>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="AC4" s="23"/>
-      <c r="AE4" s="23" t="s">
+      <c r="AC4" s="24"/>
+      <c r="AE4" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="AF4" s="23"/>
-      <c r="AG4" s="1"/>
-      <c r="AH4" s="23" t="s">
+      <c r="AF4" s="24"/>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="AI4" s="23"/>
-      <c r="AJ4" s="1"/>
-      <c r="AK4" s="23" t="s">
+      <c r="AI4" s="24"/>
+      <c r="AJ4" s="2"/>
+      <c r="AK4" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="AL4" s="23"/>
-      <c r="AM4" s="1"/>
-      <c r="AN4" s="23" t="s">
+      <c r="AL4" s="24"/>
+      <c r="AM4" s="2"/>
+      <c r="AN4" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="AO4" s="23"/>
-      <c r="AP4" s="1"/>
-      <c r="AQ4" s="23" t="s">
+      <c r="AO4" s="24"/>
+      <c r="AP4" s="2"/>
+      <c r="AQ4" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="AR4" s="23"/>
-    </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
+      <c r="AR4" s="24"/>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="25" t="n">
+      <c r="B5" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D5" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="H5" s="25" t="n">
+      <c r="H5" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="24" t="s">
+      <c r="J5" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="K5" s="25" t="n">
+      <c r="K5" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="M5" s="24" t="s">
+      <c r="M5" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="N5" s="25" t="n">
+      <c r="N5" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="P5" s="24" t="s">
+      <c r="P5" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="Q5" s="25" t="n">
+      <c r="Q5" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="R5" s="1"/>
-      <c r="S5" s="24" t="s">
+      <c r="R5" s="2"/>
+      <c r="S5" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="T5" s="25" t="n">
+      <c r="T5" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="U5" s="1"/>
-      <c r="V5" s="24" t="s">
+      <c r="U5" s="2"/>
+      <c r="V5" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="W5" s="25" t="n">
+      <c r="W5" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="24" t="s">
+      <c r="X5" s="2"/>
+      <c r="Y5" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="Z5" s="25" t="n">
+      <c r="Z5" s="26" t="n">
         <v>9</v>
       </c>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="24" t="s">
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="AC5" s="25" t="n">
+      <c r="AC5" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="AE5" s="24" t="s">
+      <c r="AE5" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="AF5" s="25" t="n">
+      <c r="AF5" s="26" t="n">
         <v>11</v>
       </c>
-      <c r="AG5" s="1"/>
-      <c r="AH5" s="24" t="s">
+      <c r="AG5" s="2"/>
+      <c r="AH5" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="AI5" s="25" t="n">
+      <c r="AI5" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="AJ5" s="1"/>
-      <c r="AK5" s="24" t="s">
+      <c r="AJ5" s="2"/>
+      <c r="AK5" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="AL5" s="25" t="n">
+      <c r="AL5" s="26" t="n">
         <v>13</v>
       </c>
-      <c r="AM5" s="1"/>
-      <c r="AN5" s="24" t="s">
+      <c r="AM5" s="2"/>
+      <c r="AN5" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="AO5" s="25" t="n">
+      <c r="AO5" s="26" t="n">
         <v>14</v>
       </c>
-      <c r="AP5" s="1"/>
-      <c r="AQ5" s="24" t="s">
+      <c r="AP5" s="2"/>
+      <c r="AQ5" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="AR5" s="25" t="n">
+      <c r="AR5" s="26" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="str">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="25" t="str">
         <f aca="false">_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>shell</v>
       </c>
-      <c r="B6" s="24"/>
-      <c r="D6" s="24" t="str">
+      <c r="B6" s="25"/>
+      <c r="D6" s="25" t="str">
         <f aca="false">_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>core</v>
       </c>
-      <c r="E6" s="24"/>
-      <c r="G6" s="24" t="str">
+      <c r="E6" s="25"/>
+      <c r="G6" s="25" t="str">
         <f aca="false">_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>foundation</v>
       </c>
-      <c r="H6" s="24"/>
-      <c r="J6" s="24" t="str">
+      <c r="H6" s="25"/>
+      <c r="J6" s="25" t="str">
         <f aca="false">_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="24"/>
-      <c r="M6" s="24" t="str">
+      <c r="K6" s="25"/>
+      <c r="M6" s="25" t="str">
         <f aca="false">_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="24"/>
-      <c r="P6" s="24" t="str">
+      <c r="N6" s="25"/>
+      <c r="P6" s="25" t="str">
         <f aca="false">_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="24" t="str">
+      <c r="Q6" s="25"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="25" t="str">
         <f aca="false">_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="24"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="24" t="str">
+      <c r="T6" s="25"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="25" t="str">
         <f aca="false">_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="24"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="24" t="str">
+      <c r="W6" s="25"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="25" t="str">
         <f aca="false">_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="24"/>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="24" t="str">
+      <c r="Z6" s="25"/>
+      <c r="AA6" s="2"/>
+      <c r="AB6" s="25" t="str">
         <f aca="false">_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="24"/>
-      <c r="AE6" s="24" t="str">
+      <c r="AC6" s="25"/>
+      <c r="AE6" s="25" t="str">
         <f aca="false">_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="24"/>
-      <c r="AG6" s="1"/>
-      <c r="AH6" s="24" t="str">
+      <c r="AF6" s="25"/>
+      <c r="AG6" s="2"/>
+      <c r="AH6" s="25" t="str">
         <f aca="false">_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="24"/>
-      <c r="AJ6" s="1"/>
-      <c r="AK6" s="24" t="str">
+      <c r="AI6" s="25"/>
+      <c r="AJ6" s="2"/>
+      <c r="AK6" s="25" t="str">
         <f aca="false">_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="24"/>
-      <c r="AM6" s="1"/>
-      <c r="AN6" s="24" t="str">
+      <c r="AL6" s="25"/>
+      <c r="AM6" s="2"/>
+      <c r="AN6" s="25" t="str">
         <f aca="false">_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="24"/>
-      <c r="AP6" s="1"/>
-      <c r="AQ6" s="24" t="str">
+      <c r="AO6" s="25"/>
+      <c r="AP6" s="2"/>
+      <c r="AQ6" s="25" t="str">
         <f aca="false">_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="24"/>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26" t="s">
+      <c r="AR6" s="25"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="H7" s="26" t="s">
+      <c r="H7" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="J7" s="26" t="s">
+      <c r="J7" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="K7" s="26" t="s">
+      <c r="K7" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="M7" s="26" t="s">
+      <c r="M7" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="N7" s="26" t="s">
+      <c r="N7" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="P7" s="26" t="s">
+      <c r="P7" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="Q7" s="26" t="s">
+      <c r="Q7" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="R7" s="1"/>
-      <c r="S7" s="26" t="s">
+      <c r="R7" s="2"/>
+      <c r="S7" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="T7" s="26" t="s">
+      <c r="T7" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="U7" s="1"/>
-      <c r="V7" s="26" t="s">
+      <c r="U7" s="2"/>
+      <c r="V7" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="W7" s="26" t="s">
+      <c r="W7" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="26" t="s">
+      <c r="X7" s="2"/>
+      <c r="Y7" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="Z7" s="26" t="s">
+      <c r="Z7" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="26" t="s">
+      <c r="AA7" s="2"/>
+      <c r="AB7" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="AC7" s="26" t="s">
+      <c r="AC7" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="AE7" s="26" t="s">
+      <c r="AE7" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="AF7" s="26" t="s">
+      <c r="AF7" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="AG7" s="1"/>
-      <c r="AH7" s="26" t="s">
+      <c r="AG7" s="2"/>
+      <c r="AH7" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="AI7" s="26" t="s">
+      <c r="AI7" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="AJ7" s="1"/>
-      <c r="AK7" s="26" t="s">
+      <c r="AJ7" s="2"/>
+      <c r="AK7" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="AL7" s="26" t="s">
+      <c r="AL7" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="AM7" s="1"/>
-      <c r="AN7" s="26" t="s">
+      <c r="AM7" s="2"/>
+      <c r="AN7" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="AO7" s="26" t="s">
+      <c r="AO7" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="AP7" s="1"/>
-      <c r="AQ7" s="26" t="s">
+      <c r="AP7" s="2"/>
+      <c r="AQ7" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="AR7" s="26" t="s">
+      <c r="AR7" s="27" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="n">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="n">
         <v>200</v>
       </c>
-      <c r="B8" s="19" t="n">
+      <c r="B8" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="20" t="n">
         <v>320</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="19" t="n">
+      <c r="H8" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="27"/>
-      <c r="T8" s="28"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="27"/>
-      <c r="W8" s="28"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="27"/>
-      <c r="Z8" s="28"/>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="27"/>
-      <c r="AC8" s="28"/>
-      <c r="AE8" s="19"/>
-      <c r="AF8" s="19"/>
-      <c r="AG8" s="1"/>
-      <c r="AH8" s="27"/>
-      <c r="AI8" s="28"/>
-      <c r="AJ8" s="1"/>
-      <c r="AK8" s="27"/>
-      <c r="AL8" s="28"/>
-      <c r="AM8" s="1"/>
-      <c r="AN8" s="27"/>
-      <c r="AO8" s="28"/>
-      <c r="AP8" s="1"/>
-      <c r="AQ8" s="27"/>
-      <c r="AR8" s="28"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="n">
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="28"/>
+      <c r="T8" s="29"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="28"/>
+      <c r="W8" s="29"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="28"/>
+      <c r="Z8" s="29"/>
+      <c r="AA8" s="2"/>
+      <c r="AB8" s="28"/>
+      <c r="AC8" s="29"/>
+      <c r="AE8" s="20"/>
+      <c r="AF8" s="20"/>
+      <c r="AG8" s="2"/>
+      <c r="AH8" s="28"/>
+      <c r="AI8" s="29"/>
+      <c r="AJ8" s="2"/>
+      <c r="AK8" s="28"/>
+      <c r="AL8" s="29"/>
+      <c r="AM8" s="2"/>
+      <c r="AN8" s="28"/>
+      <c r="AO8" s="29"/>
+      <c r="AP8" s="2"/>
+      <c r="AQ8" s="28"/>
+      <c r="AR8" s="29"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="n">
         <v>320</v>
       </c>
-      <c r="B9" s="19" t="n">
+      <c r="B9" s="20" t="n">
         <v>160</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="20" t="n">
         <v>360</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="20" t="n">
         <v>165</v>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G9" s="20" t="n">
         <v>320</v>
       </c>
-      <c r="H9" s="19" t="n">
+      <c r="H9" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="30"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="29"/>
-      <c r="W9" s="30"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="29"/>
-      <c r="Z9" s="30"/>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="29"/>
-      <c r="AC9" s="30"/>
-      <c r="AE9" s="19"/>
-      <c r="AF9" s="19"/>
-      <c r="AG9" s="1"/>
-      <c r="AH9" s="29"/>
-      <c r="AI9" s="30"/>
-      <c r="AJ9" s="1"/>
-      <c r="AK9" s="29"/>
-      <c r="AL9" s="30"/>
-      <c r="AM9" s="1"/>
-      <c r="AN9" s="29"/>
-      <c r="AO9" s="30"/>
-      <c r="AP9" s="1"/>
-      <c r="AQ9" s="29"/>
-      <c r="AR9" s="30"/>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="n">
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="31"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="31"/>
+      <c r="AA9" s="2"/>
+      <c r="AB9" s="30"/>
+      <c r="AC9" s="31"/>
+      <c r="AE9" s="20"/>
+      <c r="AF9" s="20"/>
+      <c r="AG9" s="2"/>
+      <c r="AH9" s="30"/>
+      <c r="AI9" s="31"/>
+      <c r="AJ9" s="2"/>
+      <c r="AK9" s="30"/>
+      <c r="AL9" s="31"/>
+      <c r="AM9" s="2"/>
+      <c r="AN9" s="30"/>
+      <c r="AO9" s="31"/>
+      <c r="AP9" s="2"/>
+      <c r="AQ9" s="30"/>
+      <c r="AR9" s="31"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="n">
         <v>360</v>
       </c>
-      <c r="B10" s="19" t="n">
+      <c r="B10" s="20" t="n">
         <v>180</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="20" t="n">
         <v>380</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="20" t="n">
         <v>165</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="20" t="n">
         <v>360</v>
       </c>
-      <c r="H10" s="19" t="n">
+      <c r="H10" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="29"/>
-      <c r="T10" s="30"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="29"/>
-      <c r="W10" s="30"/>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="29"/>
-      <c r="Z10" s="30"/>
-      <c r="AA10" s="1"/>
-      <c r="AB10" s="29"/>
-      <c r="AC10" s="30"/>
-      <c r="AE10" s="19"/>
-      <c r="AF10" s="19"/>
-      <c r="AG10" s="1"/>
-      <c r="AH10" s="29"/>
-      <c r="AI10" s="30"/>
-      <c r="AJ10" s="1"/>
-      <c r="AK10" s="29"/>
-      <c r="AL10" s="30"/>
-      <c r="AM10" s="1"/>
-      <c r="AN10" s="29"/>
-      <c r="AO10" s="30"/>
-      <c r="AP10" s="1"/>
-      <c r="AQ10" s="29"/>
-      <c r="AR10" s="30"/>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="n">
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="30"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="31"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="30"/>
+      <c r="Z10" s="31"/>
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="30"/>
+      <c r="AC10" s="31"/>
+      <c r="AE10" s="20"/>
+      <c r="AF10" s="20"/>
+      <c r="AG10" s="2"/>
+      <c r="AH10" s="30"/>
+      <c r="AI10" s="31"/>
+      <c r="AJ10" s="2"/>
+      <c r="AK10" s="30"/>
+      <c r="AL10" s="31"/>
+      <c r="AM10" s="2"/>
+      <c r="AN10" s="30"/>
+      <c r="AO10" s="31"/>
+      <c r="AP10" s="2"/>
+      <c r="AQ10" s="30"/>
+      <c r="AR10" s="31"/>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="n">
         <v>380</v>
       </c>
-      <c r="B11" s="19" t="n">
+      <c r="B11" s="20" t="n">
         <v>180</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="20" t="n">
         <v>420</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="20" t="n">
         <v>380</v>
       </c>
-      <c r="H11" s="19" t="n">
+      <c r="H11" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="29"/>
-      <c r="T11" s="30"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="27"/>
-      <c r="W11" s="28"/>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="29"/>
-      <c r="Z11" s="30"/>
-      <c r="AA11" s="1"/>
-      <c r="AB11" s="29"/>
-      <c r="AC11" s="30"/>
-      <c r="AE11" s="19"/>
-      <c r="AF11" s="19"/>
-      <c r="AG11" s="1"/>
-      <c r="AH11" s="29"/>
-      <c r="AI11" s="30"/>
-      <c r="AJ11" s="1"/>
-      <c r="AK11" s="29"/>
-      <c r="AL11" s="30"/>
-      <c r="AM11" s="1"/>
-      <c r="AN11" s="29"/>
-      <c r="AO11" s="30"/>
-      <c r="AP11" s="1"/>
-      <c r="AQ11" s="29"/>
-      <c r="AR11" s="30"/>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="n">
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="28"/>
+      <c r="W11" s="29"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="30"/>
+      <c r="Z11" s="31"/>
+      <c r="AA11" s="2"/>
+      <c r="AB11" s="30"/>
+      <c r="AC11" s="31"/>
+      <c r="AE11" s="20"/>
+      <c r="AF11" s="20"/>
+      <c r="AG11" s="2"/>
+      <c r="AH11" s="30"/>
+      <c r="AI11" s="31"/>
+      <c r="AJ11" s="2"/>
+      <c r="AK11" s="30"/>
+      <c r="AL11" s="31"/>
+      <c r="AM11" s="2"/>
+      <c r="AN11" s="30"/>
+      <c r="AO11" s="31"/>
+      <c r="AP11" s="2"/>
+      <c r="AQ11" s="30"/>
+      <c r="AR11" s="31"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="n">
         <v>550</v>
       </c>
-      <c r="B12" s="19" t="n">
+      <c r="B12" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="G12" s="19" t="n">
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="G12" s="20" t="n">
         <v>420</v>
       </c>
-      <c r="H12" s="19" t="n">
+      <c r="H12" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="19"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="19"/>
-      <c r="W12" s="19"/>
-      <c r="X12" s="1"/>
-      <c r="Y12" s="19"/>
-      <c r="Z12" s="19"/>
-      <c r="AA12" s="1"/>
-      <c r="AB12" s="19"/>
-      <c r="AC12" s="19"/>
-      <c r="AE12" s="19"/>
-      <c r="AF12" s="19"/>
-      <c r="AG12" s="1"/>
-      <c r="AH12" s="19"/>
-      <c r="AI12" s="19"/>
-      <c r="AJ12" s="1"/>
-      <c r="AK12" s="19"/>
-      <c r="AL12" s="19"/>
-      <c r="AM12" s="1"/>
-      <c r="AN12" s="19"/>
-      <c r="AO12" s="19"/>
-      <c r="AP12" s="1"/>
-      <c r="AQ12" s="19"/>
-      <c r="AR12" s="19"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="G13" s="19" t="n">
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="20"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="20"/>
+      <c r="W12" s="20"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="20"/>
+      <c r="Z12" s="20"/>
+      <c r="AA12" s="2"/>
+      <c r="AB12" s="20"/>
+      <c r="AC12" s="20"/>
+      <c r="AE12" s="20"/>
+      <c r="AF12" s="20"/>
+      <c r="AG12" s="2"/>
+      <c r="AH12" s="20"/>
+      <c r="AI12" s="20"/>
+      <c r="AJ12" s="2"/>
+      <c r="AK12" s="20"/>
+      <c r="AL12" s="20"/>
+      <c r="AM12" s="2"/>
+      <c r="AN12" s="20"/>
+      <c r="AO12" s="20"/>
+      <c r="AP12" s="2"/>
+      <c r="AQ12" s="20"/>
+      <c r="AR12" s="20"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="G13" s="20" t="n">
         <v>750</v>
       </c>
-      <c r="H13" s="19" t="n">
+      <c r="H13" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="19"/>
-      <c r="U13" s="1"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="19"/>
-      <c r="X13" s="1"/>
-      <c r="Y13" s="19"/>
-      <c r="Z13" s="19"/>
-      <c r="AA13" s="1"/>
-      <c r="AB13" s="19"/>
-      <c r="AC13" s="19"/>
-      <c r="AE13" s="19"/>
-      <c r="AF13" s="19"/>
-      <c r="AG13" s="1"/>
-      <c r="AH13" s="19"/>
-      <c r="AI13" s="19"/>
-      <c r="AJ13" s="1"/>
-      <c r="AK13" s="19"/>
-      <c r="AL13" s="19"/>
-      <c r="AM13" s="1"/>
-      <c r="AN13" s="19"/>
-      <c r="AO13" s="19"/>
-      <c r="AP13" s="1"/>
-      <c r="AQ13" s="19"/>
-      <c r="AR13" s="19"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="19"/>
-      <c r="R14" s="1"/>
-      <c r="S14" s="19"/>
-      <c r="T14" s="19"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="19"/>
-      <c r="W14" s="19"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="19"/>
-      <c r="Z14" s="19"/>
-      <c r="AA14" s="1"/>
-      <c r="AB14" s="19"/>
-      <c r="AC14" s="19"/>
-      <c r="AE14" s="19"/>
-      <c r="AF14" s="19"/>
-      <c r="AG14" s="1"/>
-      <c r="AH14" s="19"/>
-      <c r="AI14" s="19"/>
-      <c r="AJ14" s="1"/>
-      <c r="AK14" s="19"/>
-      <c r="AL14" s="19"/>
-      <c r="AM14" s="1"/>
-      <c r="AN14" s="19"/>
-      <c r="AO14" s="19"/>
-      <c r="AP14" s="1"/>
-      <c r="AQ14" s="19"/>
-      <c r="AR14" s="19"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19"/>
-      <c r="P15" s="19"/>
-      <c r="Q15" s="19"/>
-      <c r="R15" s="1"/>
-      <c r="S15" s="19"/>
-      <c r="T15" s="19"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="19"/>
-      <c r="W15" s="19"/>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="19"/>
-      <c r="Z15" s="19"/>
-      <c r="AA15" s="1"/>
-      <c r="AB15" s="19"/>
-      <c r="AC15" s="19"/>
-      <c r="AE15" s="19"/>
-      <c r="AF15" s="19"/>
-      <c r="AG15" s="1"/>
-      <c r="AH15" s="19"/>
-      <c r="AI15" s="19"/>
-      <c r="AJ15" s="1"/>
-      <c r="AK15" s="19"/>
-      <c r="AL15" s="19"/>
-      <c r="AM15" s="1"/>
-      <c r="AN15" s="19"/>
-      <c r="AO15" s="19"/>
-      <c r="AP15" s="1"/>
-      <c r="AQ15" s="19"/>
-      <c r="AR15" s="19"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="19"/>
-      <c r="W16" s="19"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="19"/>
-      <c r="Z16" s="19"/>
-      <c r="AA16" s="1"/>
-      <c r="AB16" s="19"/>
-      <c r="AC16" s="19"/>
-      <c r="AE16" s="19"/>
-      <c r="AF16" s="19"/>
-      <c r="AG16" s="1"/>
-      <c r="AH16" s="19"/>
-      <c r="AI16" s="19"/>
-      <c r="AJ16" s="1"/>
-      <c r="AK16" s="19"/>
-      <c r="AL16" s="19"/>
-      <c r="AM16" s="1"/>
-      <c r="AN16" s="19"/>
-      <c r="AO16" s="19"/>
-      <c r="AP16" s="1"/>
-      <c r="AQ16" s="19"/>
-      <c r="AR16" s="19"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="19"/>
-      <c r="T17" s="19"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="19"/>
-      <c r="W17" s="19"/>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="19"/>
-      <c r="Z17" s="19"/>
-      <c r="AA17" s="1"/>
-      <c r="AB17" s="19"/>
-      <c r="AC17" s="19"/>
-      <c r="AE17" s="19"/>
-      <c r="AF17" s="19"/>
-      <c r="AG17" s="1"/>
-      <c r="AH17" s="19"/>
-      <c r="AI17" s="19"/>
-      <c r="AJ17" s="1"/>
-      <c r="AK17" s="19"/>
-      <c r="AL17" s="19"/>
-      <c r="AM17" s="1"/>
-      <c r="AN17" s="19"/>
-      <c r="AO17" s="19"/>
-      <c r="AP17" s="1"/>
-      <c r="AQ17" s="19"/>
-      <c r="AR17" s="19"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="19"/>
-      <c r="W18" s="19"/>
-      <c r="X18" s="1"/>
-      <c r="Y18" s="19"/>
-      <c r="Z18" s="19"/>
-      <c r="AA18" s="1"/>
-      <c r="AB18" s="19"/>
-      <c r="AC18" s="19"/>
-      <c r="AE18" s="19"/>
-      <c r="AF18" s="19"/>
-      <c r="AG18" s="1"/>
-      <c r="AH18" s="19"/>
-      <c r="AI18" s="19"/>
-      <c r="AJ18" s="1"/>
-      <c r="AK18" s="19"/>
-      <c r="AL18" s="19"/>
-      <c r="AM18" s="1"/>
-      <c r="AN18" s="19"/>
-      <c r="AO18" s="19"/>
-      <c r="AP18" s="1"/>
-      <c r="AQ18" s="19"/>
-      <c r="AR18" s="19"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="19"/>
-      <c r="P19" s="19"/>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="19"/>
-      <c r="T19" s="19"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="19"/>
-      <c r="W19" s="19"/>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="19"/>
-      <c r="Z19" s="19"/>
-      <c r="AA19" s="1"/>
-      <c r="AB19" s="19"/>
-      <c r="AC19" s="19"/>
-      <c r="AE19" s="19"/>
-      <c r="AF19" s="19"/>
-      <c r="AG19" s="1"/>
-      <c r="AH19" s="19"/>
-      <c r="AI19" s="19"/>
-      <c r="AJ19" s="1"/>
-      <c r="AK19" s="19"/>
-      <c r="AL19" s="19"/>
-      <c r="AM19" s="1"/>
-      <c r="AN19" s="19"/>
-      <c r="AO19" s="19"/>
-      <c r="AP19" s="1"/>
-      <c r="AQ19" s="19"/>
-      <c r="AR19" s="19"/>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="19"/>
-      <c r="T20" s="19"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="19"/>
-      <c r="W20" s="19"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="19"/>
-      <c r="Z20" s="19"/>
-      <c r="AA20" s="1"/>
-      <c r="AB20" s="19"/>
-      <c r="AC20" s="19"/>
-      <c r="AE20" s="19"/>
-      <c r="AF20" s="19"/>
-      <c r="AG20" s="1"/>
-      <c r="AH20" s="19"/>
-      <c r="AI20" s="19"/>
-      <c r="AJ20" s="1"/>
-      <c r="AK20" s="19"/>
-      <c r="AL20" s="19"/>
-      <c r="AM20" s="1"/>
-      <c r="AN20" s="19"/>
-      <c r="AO20" s="19"/>
-      <c r="AP20" s="1"/>
-      <c r="AQ20" s="19"/>
-      <c r="AR20" s="19"/>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="19"/>
-      <c r="T21" s="19"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="19"/>
-      <c r="W21" s="19"/>
-      <c r="X21" s="1"/>
-      <c r="Y21" s="19"/>
-      <c r="Z21" s="19"/>
-      <c r="AA21" s="1"/>
-      <c r="AB21" s="19"/>
-      <c r="AC21" s="19"/>
-      <c r="AE21" s="19"/>
-      <c r="AF21" s="19"/>
-      <c r="AG21" s="1"/>
-      <c r="AH21" s="19"/>
-      <c r="AI21" s="19"/>
-      <c r="AJ21" s="1"/>
-      <c r="AK21" s="19"/>
-      <c r="AL21" s="19"/>
-      <c r="AM21" s="1"/>
-      <c r="AN21" s="19"/>
-      <c r="AO21" s="19"/>
-      <c r="AP21" s="1"/>
-      <c r="AQ21" s="19"/>
-      <c r="AR21" s="19"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="1"/>
-      <c r="S22" s="19"/>
-      <c r="T22" s="19"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="19"/>
-      <c r="W22" s="19"/>
-      <c r="X22" s="1"/>
-      <c r="Y22" s="19"/>
-      <c r="Z22" s="19"/>
-      <c r="AA22" s="1"/>
-      <c r="AB22" s="19"/>
-      <c r="AC22" s="19"/>
-      <c r="AE22" s="19"/>
-      <c r="AF22" s="19"/>
-      <c r="AG22" s="1"/>
-      <c r="AH22" s="19"/>
-      <c r="AI22" s="19"/>
-      <c r="AJ22" s="1"/>
-      <c r="AK22" s="19"/>
-      <c r="AL22" s="19"/>
-      <c r="AM22" s="1"/>
-      <c r="AN22" s="19"/>
-      <c r="AO22" s="19"/>
-      <c r="AP22" s="1"/>
-      <c r="AQ22" s="19"/>
-      <c r="AR22" s="19"/>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="1"/>
-      <c r="S23" s="19"/>
-      <c r="T23" s="19"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="19"/>
-      <c r="W23" s="19"/>
-      <c r="X23" s="1"/>
-      <c r="Y23" s="19"/>
-      <c r="Z23" s="19"/>
-      <c r="AA23" s="1"/>
-      <c r="AB23" s="19"/>
-      <c r="AC23" s="19"/>
-      <c r="AE23" s="19"/>
-      <c r="AF23" s="19"/>
-      <c r="AG23" s="1"/>
-      <c r="AH23" s="19"/>
-      <c r="AI23" s="19"/>
-      <c r="AJ23" s="1"/>
-      <c r="AK23" s="19"/>
-      <c r="AL23" s="19"/>
-      <c r="AM23" s="1"/>
-      <c r="AN23" s="19"/>
-      <c r="AO23" s="19"/>
-      <c r="AP23" s="1"/>
-      <c r="AQ23" s="19"/>
-      <c r="AR23" s="19"/>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="19"/>
-      <c r="T24" s="19"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="19"/>
-      <c r="W24" s="19"/>
-      <c r="X24" s="1"/>
-      <c r="Y24" s="19"/>
-      <c r="Z24" s="19"/>
-      <c r="AA24" s="1"/>
-      <c r="AB24" s="19"/>
-      <c r="AC24" s="19"/>
-      <c r="AE24" s="19"/>
-      <c r="AF24" s="19"/>
-      <c r="AG24" s="1"/>
-      <c r="AH24" s="19"/>
-      <c r="AI24" s="19"/>
-      <c r="AJ24" s="1"/>
-      <c r="AK24" s="19"/>
-      <c r="AL24" s="19"/>
-      <c r="AM24" s="1"/>
-      <c r="AN24" s="19"/>
-      <c r="AO24" s="19"/>
-      <c r="AP24" s="1"/>
-      <c r="AQ24" s="19"/>
-      <c r="AR24" s="19"/>
-    </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="19"/>
-      <c r="T25" s="19"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="19"/>
-      <c r="W25" s="19"/>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="19"/>
-      <c r="Z25" s="19"/>
-      <c r="AA25" s="1"/>
-      <c r="AB25" s="19"/>
-      <c r="AC25" s="19"/>
-      <c r="AE25" s="19"/>
-      <c r="AF25" s="19"/>
-      <c r="AG25" s="1"/>
-      <c r="AH25" s="19"/>
-      <c r="AI25" s="19"/>
-      <c r="AJ25" s="1"/>
-      <c r="AK25" s="19"/>
-      <c r="AL25" s="19"/>
-      <c r="AM25" s="1"/>
-      <c r="AN25" s="19"/>
-      <c r="AO25" s="19"/>
-      <c r="AP25" s="1"/>
-      <c r="AQ25" s="19"/>
-      <c r="AR25" s="19"/>
-    </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19"/>
-      <c r="P26" s="19"/>
-      <c r="Q26" s="19"/>
-      <c r="R26" s="1"/>
-      <c r="S26" s="19"/>
-      <c r="T26" s="19"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="19"/>
-      <c r="W26" s="19"/>
-      <c r="X26" s="1"/>
-      <c r="Y26" s="19"/>
-      <c r="Z26" s="19"/>
-      <c r="AA26" s="1"/>
-      <c r="AB26" s="19"/>
-      <c r="AC26" s="19"/>
-      <c r="AE26" s="19"/>
-      <c r="AF26" s="19"/>
-      <c r="AG26" s="1"/>
-      <c r="AH26" s="19"/>
-      <c r="AI26" s="19"/>
-      <c r="AJ26" s="1"/>
-      <c r="AK26" s="19"/>
-      <c r="AL26" s="19"/>
-      <c r="AM26" s="1"/>
-      <c r="AN26" s="19"/>
-      <c r="AO26" s="19"/>
-      <c r="AP26" s="1"/>
-      <c r="AQ26" s="19"/>
-      <c r="AR26" s="19"/>
-    </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="1"/>
-      <c r="S27" s="19"/>
-      <c r="T27" s="19"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="19"/>
-      <c r="W27" s="19"/>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="19"/>
-      <c r="Z27" s="19"/>
-      <c r="AA27" s="1"/>
-      <c r="AB27" s="19"/>
-      <c r="AC27" s="19"/>
-      <c r="AE27" s="19"/>
-      <c r="AF27" s="19"/>
-      <c r="AG27" s="1"/>
-      <c r="AH27" s="19"/>
-      <c r="AI27" s="19"/>
-      <c r="AJ27" s="1"/>
-      <c r="AK27" s="19"/>
-      <c r="AL27" s="19"/>
-      <c r="AM27" s="1"/>
-      <c r="AN27" s="19"/>
-      <c r="AO27" s="19"/>
-      <c r="AP27" s="1"/>
-      <c r="AQ27" s="19"/>
-      <c r="AR27" s="19"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="20"/>
+      <c r="Z13" s="20"/>
+      <c r="AA13" s="2"/>
+      <c r="AB13" s="20"/>
+      <c r="AC13" s="20"/>
+      <c r="AE13" s="20"/>
+      <c r="AF13" s="20"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="20"/>
+      <c r="AI13" s="20"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="20"/>
+      <c r="AL13" s="20"/>
+      <c r="AM13" s="2"/>
+      <c r="AN13" s="20"/>
+      <c r="AO13" s="20"/>
+      <c r="AP13" s="2"/>
+      <c r="AQ13" s="20"/>
+      <c r="AR13" s="20"/>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="20"/>
+      <c r="T14" s="20"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="20"/>
+      <c r="W14" s="20"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="20"/>
+      <c r="Z14" s="20"/>
+      <c r="AA14" s="2"/>
+      <c r="AB14" s="20"/>
+      <c r="AC14" s="20"/>
+      <c r="AE14" s="20"/>
+      <c r="AF14" s="20"/>
+      <c r="AG14" s="2"/>
+      <c r="AH14" s="20"/>
+      <c r="AI14" s="20"/>
+      <c r="AJ14" s="2"/>
+      <c r="AK14" s="20"/>
+      <c r="AL14" s="20"/>
+      <c r="AM14" s="2"/>
+      <c r="AN14" s="20"/>
+      <c r="AO14" s="20"/>
+      <c r="AP14" s="2"/>
+      <c r="AQ14" s="20"/>
+      <c r="AR14" s="20"/>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="20"/>
+      <c r="W15" s="20"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="20"/>
+      <c r="Z15" s="20"/>
+      <c r="AA15" s="2"/>
+      <c r="AB15" s="20"/>
+      <c r="AC15" s="20"/>
+      <c r="AE15" s="20"/>
+      <c r="AF15" s="20"/>
+      <c r="AG15" s="2"/>
+      <c r="AH15" s="20"/>
+      <c r="AI15" s="20"/>
+      <c r="AJ15" s="2"/>
+      <c r="AK15" s="20"/>
+      <c r="AL15" s="20"/>
+      <c r="AM15" s="2"/>
+      <c r="AN15" s="20"/>
+      <c r="AO15" s="20"/>
+      <c r="AP15" s="2"/>
+      <c r="AQ15" s="20"/>
+      <c r="AR15" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="20"/>
+      <c r="W16" s="20"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="20"/>
+      <c r="Z16" s="20"/>
+      <c r="AA16" s="2"/>
+      <c r="AB16" s="20"/>
+      <c r="AC16" s="20"/>
+      <c r="AE16" s="20"/>
+      <c r="AF16" s="20"/>
+      <c r="AG16" s="2"/>
+      <c r="AH16" s="20"/>
+      <c r="AI16" s="20"/>
+      <c r="AJ16" s="2"/>
+      <c r="AK16" s="20"/>
+      <c r="AL16" s="20"/>
+      <c r="AM16" s="2"/>
+      <c r="AN16" s="20"/>
+      <c r="AO16" s="20"/>
+      <c r="AP16" s="2"/>
+      <c r="AQ16" s="20"/>
+      <c r="AR16" s="20"/>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="20"/>
+      <c r="W17" s="20"/>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="20"/>
+      <c r="Z17" s="20"/>
+      <c r="AA17" s="2"/>
+      <c r="AB17" s="20"/>
+      <c r="AC17" s="20"/>
+      <c r="AE17" s="20"/>
+      <c r="AF17" s="20"/>
+      <c r="AG17" s="2"/>
+      <c r="AH17" s="20"/>
+      <c r="AI17" s="20"/>
+      <c r="AJ17" s="2"/>
+      <c r="AK17" s="20"/>
+      <c r="AL17" s="20"/>
+      <c r="AM17" s="2"/>
+      <c r="AN17" s="20"/>
+      <c r="AO17" s="20"/>
+      <c r="AP17" s="2"/>
+      <c r="AQ17" s="20"/>
+      <c r="AR17" s="20"/>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="20"/>
+      <c r="T18" s="20"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="20"/>
+      <c r="W18" s="20"/>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="20"/>
+      <c r="Z18" s="20"/>
+      <c r="AA18" s="2"/>
+      <c r="AB18" s="20"/>
+      <c r="AC18" s="20"/>
+      <c r="AE18" s="20"/>
+      <c r="AF18" s="20"/>
+      <c r="AG18" s="2"/>
+      <c r="AH18" s="20"/>
+      <c r="AI18" s="20"/>
+      <c r="AJ18" s="2"/>
+      <c r="AK18" s="20"/>
+      <c r="AL18" s="20"/>
+      <c r="AM18" s="2"/>
+      <c r="AN18" s="20"/>
+      <c r="AO18" s="20"/>
+      <c r="AP18" s="2"/>
+      <c r="AQ18" s="20"/>
+      <c r="AR18" s="20"/>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="20"/>
+      <c r="T19" s="20"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="20"/>
+      <c r="W19" s="20"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="20"/>
+      <c r="Z19" s="20"/>
+      <c r="AA19" s="2"/>
+      <c r="AB19" s="20"/>
+      <c r="AC19" s="20"/>
+      <c r="AE19" s="20"/>
+      <c r="AF19" s="20"/>
+      <c r="AG19" s="2"/>
+      <c r="AH19" s="20"/>
+      <c r="AI19" s="20"/>
+      <c r="AJ19" s="2"/>
+      <c r="AK19" s="20"/>
+      <c r="AL19" s="20"/>
+      <c r="AM19" s="2"/>
+      <c r="AN19" s="20"/>
+      <c r="AO19" s="20"/>
+      <c r="AP19" s="2"/>
+      <c r="AQ19" s="20"/>
+      <c r="AR19" s="20"/>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="20"/>
+      <c r="T20" s="20"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="20"/>
+      <c r="W20" s="20"/>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="20"/>
+      <c r="Z20" s="20"/>
+      <c r="AA20" s="2"/>
+      <c r="AB20" s="20"/>
+      <c r="AC20" s="20"/>
+      <c r="AE20" s="20"/>
+      <c r="AF20" s="20"/>
+      <c r="AG20" s="2"/>
+      <c r="AH20" s="20"/>
+      <c r="AI20" s="20"/>
+      <c r="AJ20" s="2"/>
+      <c r="AK20" s="20"/>
+      <c r="AL20" s="20"/>
+      <c r="AM20" s="2"/>
+      <c r="AN20" s="20"/>
+      <c r="AO20" s="20"/>
+      <c r="AP20" s="2"/>
+      <c r="AQ20" s="20"/>
+      <c r="AR20" s="20"/>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="20"/>
+      <c r="T21" s="20"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="20"/>
+      <c r="W21" s="20"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="20"/>
+      <c r="Z21" s="20"/>
+      <c r="AA21" s="2"/>
+      <c r="AB21" s="20"/>
+      <c r="AC21" s="20"/>
+      <c r="AE21" s="20"/>
+      <c r="AF21" s="20"/>
+      <c r="AG21" s="2"/>
+      <c r="AH21" s="20"/>
+      <c r="AI21" s="20"/>
+      <c r="AJ21" s="2"/>
+      <c r="AK21" s="20"/>
+      <c r="AL21" s="20"/>
+      <c r="AM21" s="2"/>
+      <c r="AN21" s="20"/>
+      <c r="AO21" s="20"/>
+      <c r="AP21" s="2"/>
+      <c r="AQ21" s="20"/>
+      <c r="AR21" s="20"/>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="20"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="20"/>
+      <c r="W22" s="20"/>
+      <c r="X22" s="2"/>
+      <c r="Y22" s="20"/>
+      <c r="Z22" s="20"/>
+      <c r="AA22" s="2"/>
+      <c r="AB22" s="20"/>
+      <c r="AC22" s="20"/>
+      <c r="AE22" s="20"/>
+      <c r="AF22" s="20"/>
+      <c r="AG22" s="2"/>
+      <c r="AH22" s="20"/>
+      <c r="AI22" s="20"/>
+      <c r="AJ22" s="2"/>
+      <c r="AK22" s="20"/>
+      <c r="AL22" s="20"/>
+      <c r="AM22" s="2"/>
+      <c r="AN22" s="20"/>
+      <c r="AO22" s="20"/>
+      <c r="AP22" s="2"/>
+      <c r="AQ22" s="20"/>
+      <c r="AR22" s="20"/>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="20"/>
+      <c r="W23" s="20"/>
+      <c r="X23" s="2"/>
+      <c r="Y23" s="20"/>
+      <c r="Z23" s="20"/>
+      <c r="AA23" s="2"/>
+      <c r="AB23" s="20"/>
+      <c r="AC23" s="20"/>
+      <c r="AE23" s="20"/>
+      <c r="AF23" s="20"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="20"/>
+      <c r="AI23" s="20"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="20"/>
+      <c r="AL23" s="20"/>
+      <c r="AM23" s="2"/>
+      <c r="AN23" s="20"/>
+      <c r="AO23" s="20"/>
+      <c r="AP23" s="2"/>
+      <c r="AQ23" s="20"/>
+      <c r="AR23" s="20"/>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="20"/>
+      <c r="Z24" s="20"/>
+      <c r="AA24" s="2"/>
+      <c r="AB24" s="20"/>
+      <c r="AC24" s="20"/>
+      <c r="AE24" s="20"/>
+      <c r="AF24" s="20"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="20"/>
+      <c r="AI24" s="20"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="20"/>
+      <c r="AL24" s="20"/>
+      <c r="AM24" s="2"/>
+      <c r="AN24" s="20"/>
+      <c r="AO24" s="20"/>
+      <c r="AP24" s="2"/>
+      <c r="AQ24" s="20"/>
+      <c r="AR24" s="20"/>
+    </row>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="20"/>
+      <c r="T25" s="20"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="20"/>
+      <c r="W25" s="20"/>
+      <c r="X25" s="2"/>
+      <c r="Y25" s="20"/>
+      <c r="Z25" s="20"/>
+      <c r="AA25" s="2"/>
+      <c r="AB25" s="20"/>
+      <c r="AC25" s="20"/>
+      <c r="AE25" s="20"/>
+      <c r="AF25" s="20"/>
+      <c r="AG25" s="2"/>
+      <c r="AH25" s="20"/>
+      <c r="AI25" s="20"/>
+      <c r="AJ25" s="2"/>
+      <c r="AK25" s="20"/>
+      <c r="AL25" s="20"/>
+      <c r="AM25" s="2"/>
+      <c r="AN25" s="20"/>
+      <c r="AO25" s="20"/>
+      <c r="AP25" s="2"/>
+      <c r="AQ25" s="20"/>
+      <c r="AR25" s="20"/>
+    </row>
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20"/>
+      <c r="B26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="20"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="20"/>
+      <c r="T26" s="20"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="20"/>
+      <c r="W26" s="20"/>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="20"/>
+      <c r="Z26" s="20"/>
+      <c r="AA26" s="2"/>
+      <c r="AB26" s="20"/>
+      <c r="AC26" s="20"/>
+      <c r="AE26" s="20"/>
+      <c r="AF26" s="20"/>
+      <c r="AG26" s="2"/>
+      <c r="AH26" s="20"/>
+      <c r="AI26" s="20"/>
+      <c r="AJ26" s="2"/>
+      <c r="AK26" s="20"/>
+      <c r="AL26" s="20"/>
+      <c r="AM26" s="2"/>
+      <c r="AN26" s="20"/>
+      <c r="AO26" s="20"/>
+      <c r="AP26" s="2"/>
+      <c r="AQ26" s="20"/>
+      <c r="AR26" s="20"/>
+    </row>
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="20"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="20"/>
+      <c r="T27" s="20"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="20"/>
+      <c r="W27" s="20"/>
+      <c r="X27" s="2"/>
+      <c r="Y27" s="20"/>
+      <c r="Z27" s="20"/>
+      <c r="AA27" s="2"/>
+      <c r="AB27" s="20"/>
+      <c r="AC27" s="20"/>
+      <c r="AE27" s="20"/>
+      <c r="AF27" s="20"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="20"/>
+      <c r="AI27" s="20"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="20"/>
+      <c r="AL27" s="20"/>
+      <c r="AM27" s="2"/>
+      <c r="AN27" s="20"/>
+      <c r="AO27" s="20"/>
+      <c r="AP27" s="2"/>
+      <c r="AQ27" s="20"/>
+      <c r="AR27" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -12506,156 +12510,156 @@
   <dimension ref="A2:G23"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="5.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="5.66"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="31" t="s">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="D2" s="32" t="s">
+      <c r="B2" s="32"/>
+      <c r="D2" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="32"/>
-      <c r="G2" s="33" t="s">
+      <c r="E2" s="33"/>
+      <c r="G2" s="34" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="27" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-    </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="34"/>
-      <c r="B12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="34"/>
-      <c r="B13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="34"/>
-      <c r="B14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="34"/>
-      <c r="B15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="34"/>
-      <c r="B16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="34"/>
-      <c r="B17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="34"/>
-      <c r="B18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="34"/>
-      <c r="B19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="34"/>
-      <c r="B20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="34"/>
-      <c r="B21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="34"/>
-      <c r="B22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="34"/>
-      <c r="B23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="35"/>
+      <c r="B12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="35"/>
+      <c r="B13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="35"/>
+      <c r="B14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="35"/>
+      <c r="B15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="35"/>
+      <c r="B16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="35"/>
+      <c r="B17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="35"/>
+      <c r="B18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="35"/>
+      <c r="B19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="35"/>
+      <c r="B20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="35"/>
+      <c r="B21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="35"/>
+      <c r="B22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="35"/>
+      <c r="B23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -12680,194 +12684,194 @@
   <dimension ref="A2:N16"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="2" style="1" width="10.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="47.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="6.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="2" style="2" width="10.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="47.85"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="35" t="s">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="D2" s="35" t="s">
+      <c r="D2" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="E2" s="35" t="s">
+      <c r="E2" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="G2" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="H2" s="35" t="s">
+      <c r="H2" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="K2" s="36" t="s">
+      <c r="K2" s="37" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="n">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="19" t="n">
+      <c r="B3" s="20" t="n">
         <v>500</v>
       </c>
-      <c r="C3" s="19" t="n">
+      <c r="C3" s="20" t="n">
         <v>200</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="E3" s="19" t="n">
+      <c r="E3" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="J3" s="1" t="s">
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="J3" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="9" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="n">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="J4" s="1" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="J4" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="9" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="n">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="J5" s="1" t="s">
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="J5" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="K5" s="0" t="s">
+      <c r="K5" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="n">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="n">
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="n">
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="n">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="n">
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="n">
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="n">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H3:H42">
@@ -12909,150 +12913,150 @@
   <dimension ref="A2:F23"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="10.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="33.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="2" width="10.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="13.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="33.66"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="37" t="s">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="E3" s="0" t="s">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="E3" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="E4" s="0" t="s">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="E4" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="E5" s="0" t="s">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="E5" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -13079,507 +13083,507 @@
   <dimension ref="B2:X22"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="7.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="7.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="10" style="0" width="7.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="14" style="0" width="7.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="18" style="0" width="7.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="22" style="0" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="10" style="1" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="14" style="1" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="18" style="1" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="22" style="1" width="7.66"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="39" t="s">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="F2" s="39" t="s">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="F2" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="J2" s="39" t="s">
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="J2" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="N2" s="39" t="s">
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="N2" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="R2" s="39" t="s">
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="R2" s="40" t="s">
         <v>123</v>
       </c>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="V2" s="39" t="s">
+      <c r="S2" s="40"/>
+      <c r="T2" s="40"/>
+      <c r="V2" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="W2" s="39"/>
-      <c r="X2" s="39"/>
-    </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="26" t="s">
+      <c r="W2" s="40"/>
+      <c r="X2" s="40"/>
+    </row>
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="H3" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="J3" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K3" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="L3" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="26" t="s">
+      <c r="N3" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="O3" s="26" t="s">
+      <c r="O3" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="P3" s="26" t="s">
+      <c r="P3" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="R3" s="26" t="s">
+      <c r="R3" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="S3" s="26" t="s">
+      <c r="S3" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="T3" s="26" t="s">
+      <c r="T3" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="V3" s="26" t="s">
+      <c r="V3" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="W3" s="26" t="s">
+      <c r="W3" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="X3" s="26" t="s">
+      <c r="X3" s="27" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="19" t="n">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="19" t="n">
+      <c r="C4" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="D4" s="19" t="n">
+      <c r="D4" s="20" t="n">
         <f aca="false">60*62.4</f>
         <v>3744</v>
       </c>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
-      <c r="T4" s="19"/>
-      <c r="V4" s="19"/>
-      <c r="W4" s="19"/>
-      <c r="X4" s="19"/>
-    </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="19" t="n">
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
+      <c r="V4" s="20"/>
+      <c r="W4" s="20"/>
+      <c r="X4" s="20"/>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="20" t="n">
         <v>200</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="20" t="n">
         <f aca="false">D4</f>
         <v>3744</v>
       </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="R5" s="19"/>
-      <c r="S5" s="19"/>
-      <c r="T5" s="19"/>
-      <c r="V5" s="19"/>
-      <c r="W5" s="19"/>
-      <c r="X5" s="19"/>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="19" t="n">
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="20"/>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="20" t="n">
         <v>320</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="20" t="n">
         <v>160</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
-      <c r="T6" s="19"/>
-      <c r="V6" s="19"/>
-      <c r="W6" s="19"/>
-      <c r="X6" s="19"/>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19"/>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="19"/>
-      <c r="X7" s="19"/>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="19"/>
-      <c r="V8" s="19"/>
-      <c r="W8" s="19"/>
-      <c r="X8" s="19"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="19"/>
-      <c r="T9" s="19"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="19"/>
-      <c r="X9" s="19"/>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="R10" s="19"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="19"/>
-      <c r="V10" s="19"/>
-      <c r="W10" s="19"/>
-      <c r="X10" s="19"/>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="19"/>
-      <c r="V11" s="19"/>
-      <c r="W11" s="19"/>
-      <c r="X11" s="19"/>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
-      <c r="R12" s="19"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="19"/>
-      <c r="V12" s="19"/>
-      <c r="W12" s="19"/>
-      <c r="X12" s="19"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="R13" s="19"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="19"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="19"/>
-      <c r="X13" s="19"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="R14" s="19"/>
-      <c r="S14" s="19"/>
-      <c r="T14" s="19"/>
-      <c r="V14" s="19"/>
-      <c r="W14" s="19"/>
-      <c r="X14" s="19"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="P15" s="19"/>
-      <c r="R15" s="19"/>
-      <c r="S15" s="19"/>
-      <c r="T15" s="19"/>
-      <c r="V15" s="19"/>
-      <c r="W15" s="19"/>
-      <c r="X15" s="19"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="R16" s="19"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
-      <c r="V16" s="19"/>
-      <c r="W16" s="19"/>
-      <c r="X16" s="19"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="R17" s="19"/>
-      <c r="S17" s="19"/>
-      <c r="T17" s="19"/>
-      <c r="V17" s="19"/>
-      <c r="W17" s="19"/>
-      <c r="X17" s="19"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="R18" s="19"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-      <c r="V18" s="19"/>
-      <c r="W18" s="19"/>
-      <c r="X18" s="19"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
-      <c r="R19" s="19"/>
-      <c r="S19" s="19"/>
-      <c r="T19" s="19"/>
-      <c r="V19" s="19"/>
-      <c r="W19" s="19"/>
-      <c r="X19" s="19"/>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="R20" s="19"/>
-      <c r="S20" s="19"/>
-      <c r="T20" s="19"/>
-      <c r="V20" s="19"/>
-      <c r="W20" s="19"/>
-      <c r="X20" s="19"/>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="R21" s="19"/>
-      <c r="S21" s="19"/>
-      <c r="T21" s="19"/>
-      <c r="V21" s="19"/>
-      <c r="W21" s="19"/>
-      <c r="X21" s="19"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="R22" s="19"/>
-      <c r="S22" s="19"/>
-      <c r="T22" s="19"/>
-      <c r="V22" s="19"/>
-      <c r="W22" s="19"/>
-      <c r="X22" s="19"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="20"/>
+      <c r="X6" s="20"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20"/>
+      <c r="X7" s="20"/>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="20"/>
+      <c r="T8" s="20"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="20"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="20"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="20"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="20"/>
+      <c r="V12" s="20"/>
+      <c r="W12" s="20"/>
+      <c r="X12" s="20"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="20"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="20"/>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="20"/>
+      <c r="T14" s="20"/>
+      <c r="V14" s="20"/>
+      <c r="W14" s="20"/>
+      <c r="X14" s="20"/>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="20"/>
+      <c r="V15" s="20"/>
+      <c r="W15" s="20"/>
+      <c r="X15" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+      <c r="V16" s="20"/>
+      <c r="W16" s="20"/>
+      <c r="X16" s="20"/>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="20"/>
+      <c r="V17" s="20"/>
+      <c r="W17" s="20"/>
+      <c r="X17" s="20"/>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="R18" s="20"/>
+      <c r="S18" s="20"/>
+      <c r="T18" s="20"/>
+      <c r="V18" s="20"/>
+      <c r="W18" s="20"/>
+      <c r="X18" s="20"/>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="20"/>
+      <c r="T19" s="20"/>
+      <c r="V19" s="20"/>
+      <c r="W19" s="20"/>
+      <c r="X19" s="20"/>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="20"/>
+      <c r="T20" s="20"/>
+      <c r="V20" s="20"/>
+      <c r="W20" s="20"/>
+      <c r="X20" s="20"/>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="20"/>
+      <c r="T21" s="20"/>
+      <c r="V21" s="20"/>
+      <c r="W21" s="20"/>
+      <c r="X21" s="20"/>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="R22" s="20"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="20"/>
+      <c r="V22" s="20"/>
+      <c r="W22" s="20"/>
+      <c r="X22" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -13608,487 +13612,487 @@
   <dimension ref="B2:X22"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="7.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="7.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="10" style="0" width="7.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="14" style="0" width="7.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="18" style="0" width="7.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="22" style="0" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="10" style="1" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="14" style="1" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="18" style="1" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="22" style="1" width="7.66"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="40" t="s">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="F2" s="40" t="s">
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="F2" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="J2" s="40" t="s">
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="J2" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="N2" s="40" t="s">
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="N2" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="R2" s="40" t="s">
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="R2" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="S2" s="40"/>
-      <c r="T2" s="40"/>
-      <c r="V2" s="40" t="s">
+      <c r="S2" s="41"/>
+      <c r="T2" s="41"/>
+      <c r="V2" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="W2" s="40"/>
-      <c r="X2" s="40"/>
-    </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="26" t="s">
+      <c r="W2" s="41"/>
+      <c r="X2" s="41"/>
+    </row>
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="H3" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="J3" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K3" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="L3" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="26" t="s">
+      <c r="N3" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="O3" s="26" t="s">
+      <c r="O3" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="P3" s="26" t="s">
+      <c r="P3" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="R3" s="26" t="s">
+      <c r="R3" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="S3" s="26" t="s">
+      <c r="S3" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="T3" s="26" t="s">
+      <c r="T3" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="V3" s="26" t="s">
+      <c r="V3" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="W3" s="26" t="s">
+      <c r="W3" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="X3" s="26" t="s">
+      <c r="X3" s="27" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
-      <c r="T4" s="19"/>
-      <c r="V4" s="19"/>
-      <c r="W4" s="19"/>
-      <c r="X4" s="19"/>
-    </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="R5" s="19"/>
-      <c r="S5" s="19"/>
-      <c r="T5" s="19"/>
-      <c r="V5" s="19"/>
-      <c r="W5" s="19"/>
-      <c r="X5" s="19"/>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
-      <c r="T6" s="19"/>
-      <c r="V6" s="19"/>
-      <c r="W6" s="19"/>
-      <c r="X6" s="19"/>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19"/>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="19"/>
-      <c r="X7" s="19"/>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="19"/>
-      <c r="V8" s="19"/>
-      <c r="W8" s="19"/>
-      <c r="X8" s="19"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="19"/>
-      <c r="T9" s="19"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="19"/>
-      <c r="X9" s="19"/>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="R10" s="19"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="19"/>
-      <c r="V10" s="19"/>
-      <c r="W10" s="19"/>
-      <c r="X10" s="19"/>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="19"/>
-      <c r="V11" s="19"/>
-      <c r="W11" s="19"/>
-      <c r="X11" s="19"/>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
-      <c r="R12" s="19"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="19"/>
-      <c r="V12" s="19"/>
-      <c r="W12" s="19"/>
-      <c r="X12" s="19"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="R13" s="19"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="19"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="19"/>
-      <c r="X13" s="19"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="R14" s="19"/>
-      <c r="S14" s="19"/>
-      <c r="T14" s="19"/>
-      <c r="V14" s="19"/>
-      <c r="W14" s="19"/>
-      <c r="X14" s="19"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="P15" s="19"/>
-      <c r="R15" s="19"/>
-      <c r="S15" s="19"/>
-      <c r="T15" s="19"/>
-      <c r="V15" s="19"/>
-      <c r="W15" s="19"/>
-      <c r="X15" s="19"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="R16" s="19"/>
-      <c r="S16" s="19"/>
-      <c r="T16" s="19"/>
-      <c r="V16" s="19"/>
-      <c r="W16" s="19"/>
-      <c r="X16" s="19"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="R17" s="19"/>
-      <c r="S17" s="19"/>
-      <c r="T17" s="19"/>
-      <c r="V17" s="19"/>
-      <c r="W17" s="19"/>
-      <c r="X17" s="19"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="R18" s="19"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-      <c r="V18" s="19"/>
-      <c r="W18" s="19"/>
-      <c r="X18" s="19"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
-      <c r="R19" s="19"/>
-      <c r="S19" s="19"/>
-      <c r="T19" s="19"/>
-      <c r="V19" s="19"/>
-      <c r="W19" s="19"/>
-      <c r="X19" s="19"/>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="R20" s="19"/>
-      <c r="S20" s="19"/>
-      <c r="T20" s="19"/>
-      <c r="V20" s="19"/>
-      <c r="W20" s="19"/>
-      <c r="X20" s="19"/>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="R21" s="19"/>
-      <c r="S21" s="19"/>
-      <c r="T21" s="19"/>
-      <c r="V21" s="19"/>
-      <c r="W21" s="19"/>
-      <c r="X21" s="19"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="R22" s="19"/>
-      <c r="S22" s="19"/>
-      <c r="T22" s="19"/>
-      <c r="V22" s="19"/>
-      <c r="W22" s="19"/>
-      <c r="X22" s="19"/>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
+      <c r="V4" s="20"/>
+      <c r="W4" s="20"/>
+      <c r="X4" s="20"/>
+    </row>
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="20"/>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="20"/>
+      <c r="X6" s="20"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20"/>
+      <c r="X7" s="20"/>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="20"/>
+      <c r="T8" s="20"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="20"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="20"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="20"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="20"/>
+      <c r="V12" s="20"/>
+      <c r="W12" s="20"/>
+      <c r="X12" s="20"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="20"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="20"/>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="20"/>
+      <c r="T14" s="20"/>
+      <c r="V14" s="20"/>
+      <c r="W14" s="20"/>
+      <c r="X14" s="20"/>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="20"/>
+      <c r="V15" s="20"/>
+      <c r="W15" s="20"/>
+      <c r="X15" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+      <c r="V16" s="20"/>
+      <c r="W16" s="20"/>
+      <c r="X16" s="20"/>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="20"/>
+      <c r="V17" s="20"/>
+      <c r="W17" s="20"/>
+      <c r="X17" s="20"/>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="R18" s="20"/>
+      <c r="S18" s="20"/>
+      <c r="T18" s="20"/>
+      <c r="V18" s="20"/>
+      <c r="W18" s="20"/>
+      <c r="X18" s="20"/>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="20"/>
+      <c r="T19" s="20"/>
+      <c r="V19" s="20"/>
+      <c r="W19" s="20"/>
+      <c r="X19" s="20"/>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="20"/>
+      <c r="T20" s="20"/>
+      <c r="V20" s="20"/>
+      <c r="W20" s="20"/>
+      <c r="X20" s="20"/>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="20"/>
+      <c r="T21" s="20"/>
+      <c r="V21" s="20"/>
+      <c r="W21" s="20"/>
+      <c r="X21" s="20"/>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="R22" s="20"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="20"/>
+      <c r="V22" s="20"/>
+      <c r="W22" s="20"/>
+      <c r="X22" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/docs/seep/files/xslope_johnson_res.xlsx
+++ b/docs/seep/files/xslope_johnson_res.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11708D50-B4AE-4447-916E-877A7873BC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC02AEA9-EA56-1649-9CD0-1ADB754CC06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33220" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18260" yWindow="3440" windowWidth="44060" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -223,6 +223,12 @@
     <t>Water loads:</t>
   </si>
   <si>
+    <t>auto</t>
+  </si>
+  <si>
+    <t>Surface family:</t>
+  </si>
+  <si>
     <t>Unit Options:</t>
   </si>
   <si>
@@ -397,9 +403,6 @@
     <t>g</t>
   </si>
   <si>
-    <t>gsat</t>
-  </si>
-  <si>
     <t>option</t>
   </si>
   <si>
@@ -463,24 +466,9 @@
     <t>hb_d</t>
   </si>
   <si>
-    <t>s(g)</t>
-  </si>
-  <si>
-    <t>s(c)</t>
-  </si>
-  <si>
     <t>s(f)</t>
   </si>
   <si>
-    <t>s(c/p)</t>
-  </si>
-  <si>
-    <t>s(d)</t>
-  </si>
-  <si>
-    <t>s(psi)</t>
-  </si>
-  <si>
     <t>k1</t>
   </si>
   <si>
@@ -874,9 +862,6 @@
     <t>H</t>
   </si>
   <si>
-    <t>qp</t>
-  </si>
-  <si>
     <t>D</t>
   </si>
   <si>
@@ -991,7 +976,143 @@
     <t>save_times</t>
   </si>
   <si>
-    <t>auto</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(c)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>g</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(c/p)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(d)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>s(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>psi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>g</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>sat</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1453,16 +1574,16 @@
     <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1756,6 +1877,570 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>217714</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>54430</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>199571</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>9071</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B0FB8E9-E4E3-974A-BE46-8E599C58A56D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14804571" y="254001"/>
+          <a:ext cx="3610429" cy="3746499"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Label</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = name used in error messages, summaries, and plots</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>(x1, y1), (x2, y2) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t>= start and end of reinforcement line</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="1"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Type</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = support preset, fills Dir and Appl: Geosynthetic (Tangent, Active), Nail (Axial, Passive), Tieback (Axial, Active), Anchor (Axial, Active)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Dir</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = force direction at the slip surface (LEM only): Tangent = reorients along slip surface (flexible); Axial = along the reinforcement line (rigid). Set by Type; overtype to override.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Appl</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = force application (LEM only): Active = allowable force, not divided by FS (default). Passive = ultimate force, divided by FS. Set by Type; overtype to override.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Tmax</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = tensile capacity (force/length; or force per element if Spacing is given)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Lp1, Lp2 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t>= pullout length at end 1 / end 2 (0 = fully anchored)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Tend1, Tend2 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t>= anchorage/plate/connection capacity at end 1 / end 2 (0 = friction only)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Spacing</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = out-of-plane spacing for discrete supports (nails, tiebacks); blank or 1 for geosynthetics</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Tres</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = residual capacity after rupture (FEM only)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>E</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = modulus of elasticity of reinforcement (FEM only)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Area</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = cross-sectional area of reinforcement (FEM only)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>308429</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>571501</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>145143</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6B716B0-439A-6440-8742-7BC140EF924C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13398500" y="190499"/>
+          <a:ext cx="3156858" cy="2349501"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>(x1,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t> y1), (x2, y2) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>= top and bottom of pile</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>H</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> = Pile force magnitude (kN/m or lb/ft). </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>appl</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = force application (LEM only): Active = allowable force, not divided by FS (default). Passive = ultimate force, divided by FS.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>D</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t> = </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Pile diameter</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> (ft or m)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>S</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t> = center to center pile spacing</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> (ft or m)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Vcap</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Shear</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> capacity of pile (force)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Mcap</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Moment capacity of pile (force x length)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>E</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> = Young's modulus of pile material (force/lengh^2)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>I </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t>= </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Moment of inertia (length^4)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>Area</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> = </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Cross-sectional area (length^2)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Fixity</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Pile head status (fixed or free)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2100,15 +2785,15 @@
         <v>2</v>
       </c>
       <c r="D5" s="30">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
       <c r="F7" s="15" t="s">
         <v>4</v>
       </c>
@@ -2136,7 +2821,11 @@
       <c r="C9" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="1"/>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="F9" s="1" t="s">
         <v>12</v>
       </c>
@@ -2318,15 +3007,19 @@
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B24" s="1"/>
+      <c r="C24" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24"/>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D49" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D50" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="4:4" x14ac:dyDescent="0.2">
@@ -2336,22 +3029,22 @@
     </row>
     <row r="53" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D53" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D54" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D55" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D56" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="4:4" x14ac:dyDescent="0.2">
@@ -2361,7 +3054,7 @@
     </row>
     <row r="59" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D59" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="4:4" x14ac:dyDescent="0.2">
@@ -2371,89 +3064,89 @@
     </row>
     <row r="61" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D61" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D63" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="64" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D64" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D65" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D66" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D67" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D68" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D69" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D70" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D71" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="73" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D73" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="74" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D74" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="75" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D75" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D76" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="77" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D77" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D78" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B7:D7"/>
   </mergeCells>
-  <dataValidations count="7">
+  <dataValidations count="8">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D22" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"rollers,fixed"</formula1>
     </dataValidation>
@@ -2475,6 +3168,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"auto,manual"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D24" xr:uid="{00000000-0002-0000-0000-000007000000}">
+      <formula1>"circular,non-circular"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2495,67 +3191,67 @@
   <sheetData>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="G2" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="H2" s="40" t="s">
         <v>248</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="I2" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="J2" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="K2" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="L2" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="M2" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="N2" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="O2" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="P2" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="Q2" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="R2" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="Z2" t="s">
         <v>258</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="AA2" t="s">
         <v>259</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="AB2" t="s">
         <v>260</v>
-      </c>
-      <c r="Q2" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="R2" s="28" t="s">
-        <v>261</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>262</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>263</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
@@ -2586,13 +3282,13 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="Z3" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="AA3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="AB3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
@@ -2623,7 +3319,7 @@
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="Z4" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -2654,7 +3350,7 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="Z5" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -2741,13 +3437,13 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="Z8" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="AA8" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="AB8" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
@@ -2778,13 +3474,13 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="Z9" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="AA9" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="AB9" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
@@ -2815,13 +3511,13 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="Z10" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AA10" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="AB10" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
@@ -2852,13 +3548,13 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="Z11" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AA11" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="AB11" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -3172,7 +3868,7 @@
     <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="T23" s="42"/>
       <c r="U23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.2">
@@ -3180,7 +3876,7 @@
       <c r="L24" s="9"/>
       <c r="T24" s="26"/>
       <c r="U24" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.2">
@@ -3188,7 +3884,7 @@
       <c r="L25" s="9"/>
       <c r="T25" s="29"/>
       <c r="U25" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -3204,82 +3900,80 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A2:AA18"/>
+  <dimension ref="A2:Z17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="1" customWidth="1"/>
-    <col min="3" max="8" width="10.83203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5" customWidth="1"/>
-    <col min="10" max="17" width="10.83203125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="5.5" customWidth="1"/>
+    <col min="3" max="7" width="10.83203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" customWidth="1"/>
+    <col min="9" max="16" width="10.83203125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="E2" s="12" t="s">
+      <c r="G2" s="40" t="s">
+        <v>266</v>
+      </c>
+      <c r="H2" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="G2" s="40" t="s">
+      <c r="I2" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="K2" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="L2" s="41" t="s">
         <v>270</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="M2" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="N2" s="28" t="s">
         <v>271</v>
       </c>
-      <c r="I2" s="40" t="s">
-        <v>253</v>
-      </c>
-      <c r="J2" s="27" t="s">
+      <c r="O2" s="28" t="s">
+        <v>257</v>
+      </c>
+      <c r="P2" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="K2" s="27" t="s">
-        <v>273</v>
-      </c>
-      <c r="L2" s="41" t="s">
-        <v>274</v>
-      </c>
-      <c r="M2" s="41" t="s">
-        <v>275</v>
-      </c>
-      <c r="N2" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="O2" s="28" t="s">
-        <v>276</v>
-      </c>
-      <c r="P2" s="28" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q2" s="28" t="s">
-        <v>277</v>
+      <c r="Y2" t="s">
+        <v>222</v>
       </c>
       <c r="Z2" t="s">
-        <v>226</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -3298,15 +3992,14 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
+      <c r="Y3" t="s">
+        <v>226</v>
+      </c>
       <c r="Z3" t="s">
-        <v>230</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -3325,9 +4018,8 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -3346,9 +4038,8 @@
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -3367,9 +4058,8 @@
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -3388,9 +4078,8 @@
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -3409,9 +4098,8 @@
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -3430,9 +4118,8 @@
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -3451,9 +4138,8 @@
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -3472,9 +4158,8 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -3493,44 +4178,40 @@
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="I14" s="9"/>
       <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="S16" s="42"/>
-      <c r="T16" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="19:20" x14ac:dyDescent="0.2">
-      <c r="S17" s="26"/>
-      <c r="T17" s="9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18" spans="19:20" x14ac:dyDescent="0.2">
-      <c r="S18" s="29"/>
-      <c r="T18" s="9" t="s">
-        <v>102</v>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="R15" s="42"/>
+      <c r="S15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="R16" s="26"/>
+      <c r="S16" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="18:19" x14ac:dyDescent="0.2">
+      <c r="R17" s="29"/>
+      <c r="S17" s="9" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q3:Q12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+      <formula1>$Y$2:$Y$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
       <formula1>$Z$2:$Z$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
-      <formula1>$AA$2:$AA$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3546,22 +4227,22 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -3784,29 +4465,29 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="64" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="59" t="s">
-        <v>281</v>
-      </c>
-      <c r="F2" s="54"/>
+        <v>276</v>
+      </c>
+      <c r="F2" s="52"/>
       <c r="H2" s="59" t="s">
-        <v>282</v>
-      </c>
-      <c r="I2" s="54"/>
+        <v>277</v>
+      </c>
+      <c r="I2" s="52"/>
       <c r="K2" s="59" t="s">
-        <v>283</v>
-      </c>
-      <c r="L2" s="54"/>
+        <v>278</v>
+      </c>
+      <c r="L2" s="52"/>
       <c r="N2" s="59" t="s">
-        <v>284</v>
-      </c>
-      <c r="O2" s="54"/>
+        <v>279</v>
+      </c>
+      <c r="O2" s="52"/>
       <c r="Q2" s="59" t="s">
-        <v>285</v>
-      </c>
-      <c r="R2" s="54"/>
+        <v>280</v>
+      </c>
+      <c r="R2" s="52"/>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B3" s="66"/>
@@ -3828,63 +4509,63 @@
         <v>100.0</v>
       </c>
       <c r="K3" s="32" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="L3" s="33"/>
       <c r="N3" s="32" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="O3" s="33"/>
       <c r="Q3" s="32" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="R3" s="33"/>
       <c r="T3" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="K4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="L4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="N4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="O4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="Q4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="R4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="U4" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -3913,10 +4594,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="U5" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -3945,7 +4626,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="T6" s="1" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="U6" s="9"/>
     </row>
@@ -4238,99 +4919,99 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="68" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="60" t="s">
-        <v>293</v>
-      </c>
-      <c r="F2" s="54"/>
+        <v>288</v>
+      </c>
+      <c r="F2" s="52"/>
       <c r="H2" s="60" t="s">
-        <v>294</v>
-      </c>
-      <c r="I2" s="54"/>
+        <v>289</v>
+      </c>
+      <c r="I2" s="52"/>
       <c r="K2" s="60" t="s">
-        <v>295</v>
-      </c>
-      <c r="L2" s="54"/>
+        <v>290</v>
+      </c>
+      <c r="L2" s="52"/>
       <c r="N2" s="60" t="s">
-        <v>296</v>
-      </c>
-      <c r="O2" s="54"/>
+        <v>291</v>
+      </c>
+      <c r="O2" s="52"/>
       <c r="Q2" s="60" t="s">
-        <v>297</v>
-      </c>
-      <c r="R2" s="54"/>
+        <v>292</v>
+      </c>
+      <c r="R2" s="52"/>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B3" s="66"/>
       <c r="C3" s="67"/>
       <c r="E3" s="34" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="F3" s="35"/>
       <c r="H3" s="34" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="I3" s="35"/>
       <c r="K3" s="34" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="L3" s="35"/>
       <c r="N3" s="34" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="O3" s="35"/>
       <c r="Q3" s="34" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="R3" s="35"/>
       <c r="T3" s="6" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="K4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="L4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="N4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="O4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="Q4" s="25" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="R4" s="25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="U4" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -4347,10 +5028,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="U5" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -4649,22 +5330,22 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B2" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>294</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>295</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>296</v>
+      </c>
+      <c r="F2" s="50" t="s">
+        <v>297</v>
+      </c>
+      <c r="G2" s="50" t="s">
         <v>298</v>
-      </c>
-      <c r="C2" s="50" t="s">
-        <v>299</v>
-      </c>
-      <c r="D2" s="50" t="s">
-        <v>300</v>
-      </c>
-      <c r="E2" s="50" t="s">
-        <v>301</v>
-      </c>
-      <c r="F2" s="50" t="s">
-        <v>302</v>
-      </c>
-      <c r="G2" s="50" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
@@ -4675,7 +5356,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="I3" s="14" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -4697,7 +5378,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="I5" s="14" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -4719,7 +5400,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="I7" s="14" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -4731,7 +5412,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="I8" s="14" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -4743,7 +5424,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="14" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -4763,7 +5444,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="J11" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
@@ -5585,294 +6266,294 @@
   <sheetData>
     <row r="2" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C2" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AD2" s="6"/>
       <c r="AJ2" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C3" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AD3" s="14"/>
       <c r="AJ3" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AK3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L4" s="42"/>
       <c r="M4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>18</v>
       </c>
       <c r="P4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AD4" s="14"/>
       <c r="AJ4" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AK4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L5" s="26"/>
       <c r="M5" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P5" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AD5" s="14"/>
       <c r="AJ5" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK5" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C6" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L6" s="29"/>
       <c r="M6" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="P6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="C9" s="53" t="s">
-        <v>107</v>
-      </c>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="52"/>
-      <c r="K9" s="54"/>
-      <c r="L9" s="54"/>
-      <c r="M9" s="54"/>
-      <c r="N9" s="54"/>
-      <c r="O9" s="54"/>
-      <c r="P9" s="54"/>
-      <c r="Q9" s="54"/>
-      <c r="R9" s="54"/>
-      <c r="S9" s="54"/>
-      <c r="T9" s="54"/>
-      <c r="U9" s="54"/>
-      <c r="V9" s="54"/>
-      <c r="W9" s="54"/>
-      <c r="X9" s="54"/>
-      <c r="Y9" s="54"/>
-      <c r="Z9" s="54"/>
-      <c r="AA9" s="53" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB9" s="54"/>
-      <c r="AC9" s="54"/>
-      <c r="AD9" s="54"/>
-      <c r="AE9" s="54"/>
-      <c r="AF9" s="54"/>
-      <c r="AG9" s="53" t="s">
+      <c r="C9" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="AH9" s="54"/>
-      <c r="AI9" s="54"/>
-      <c r="AJ9" s="54"/>
-      <c r="AK9" s="54"/>
-      <c r="AL9" s="54"/>
-      <c r="AM9" s="54"/>
-      <c r="AN9" s="54"/>
-      <c r="AO9" s="54"/>
-      <c r="AP9" s="54"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="53"/>
+      <c r="K9" s="52"/>
+      <c r="L9" s="52"/>
+      <c r="M9" s="52"/>
+      <c r="N9" s="52"/>
+      <c r="O9" s="52"/>
+      <c r="P9" s="52"/>
+      <c r="Q9" s="52"/>
+      <c r="R9" s="52"/>
+      <c r="S9" s="52"/>
+      <c r="T9" s="52"/>
+      <c r="U9" s="52"/>
+      <c r="V9" s="52"/>
+      <c r="W9" s="52"/>
+      <c r="X9" s="52"/>
+      <c r="Y9" s="52"/>
+      <c r="Z9" s="52"/>
+      <c r="AA9" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB9" s="52"/>
+      <c r="AC9" s="52"/>
+      <c r="AD9" s="52"/>
+      <c r="AE9" s="52"/>
+      <c r="AF9" s="52"/>
+      <c r="AG9" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="AH9" s="52"/>
+      <c r="AI9" s="52"/>
+      <c r="AJ9" s="52"/>
+      <c r="AK9" s="52"/>
+      <c r="AL9" s="52"/>
+      <c r="AM9" s="52"/>
+      <c r="AN9" s="52"/>
+      <c r="AO9" s="52"/>
+      <c r="AP9" s="52"/>
     </row>
     <row r="10" spans="1:42" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>112</v>
+        <v>310</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F10" s="44" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G10" s="45" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H10" s="44" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I10" s="44" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J10" s="49" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K10" s="49" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M10" s="21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N10" s="43" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O10" s="44" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P10" s="44" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q10" s="44" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R10" s="44" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="S10" s="44" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="T10" s="44" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="U10" s="44" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="V10" s="44" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="W10" s="44" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="X10" s="44" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Y10" s="44" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Z10" s="44" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AA10" s="46" t="s">
-        <v>134</v>
+        <v>306</v>
       </c>
       <c r="AB10" s="46" t="s">
+        <v>305</v>
+      </c>
+      <c r="AC10" s="47" t="s">
         <v>135</v>
       </c>
-      <c r="AC10" s="47" t="s">
+      <c r="AD10" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="AE10" s="46" t="s">
+        <v>308</v>
+      </c>
+      <c r="AF10" s="47" t="s">
+        <v>309</v>
+      </c>
+      <c r="AG10" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="AD10" s="46" t="s">
+      <c r="AH10" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="AE10" s="46" t="s">
+      <c r="AI10" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="AF10" s="47" t="s">
+      <c r="AJ10" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="AG10" s="23" t="s">
+      <c r="AK10" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="AH10" s="23" t="s">
+      <c r="AL10" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="AI10" s="23" t="s">
+      <c r="AM10" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="AJ10" s="23" t="s">
+      <c r="AN10" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="AK10" s="23" t="s">
+      <c r="AO10" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="AL10" s="23" t="s">
+      <c r="AP10" s="23" t="s">
         <v>145</v>
-      </c>
-      <c r="AM10" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="AN10" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="AO10" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="AP10" s="23" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.2">
@@ -7587,16 +8268,16 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B2" s="3">
         <v>0.0</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="N2" s="24" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
@@ -7605,171 +8286,171 @@
           <t>Profile Line #1</t>
         </is>
       </c>
-      <c r="B4" s="52"/>
+      <c r="B4" s="53"/>
       <c r="D4" s="55" t="inlineStr">
         <is>
           <t>Profile Line #2</t>
         </is>
       </c>
-      <c r="E4" s="52"/>
+      <c r="E4" s="53"/>
       <c r="G4" s="55" t="inlineStr">
         <is>
           <t>Profile Line #3</t>
         </is>
       </c>
-      <c r="H4" s="52"/>
+      <c r="H4" s="53"/>
       <c r="J4" s="55" t="s">
-        <v>156</v>
-      </c>
-      <c r="K4" s="52"/>
+        <v>152</v>
+      </c>
+      <c r="K4" s="53"/>
       <c r="M4" s="55" t="s">
-        <v>157</v>
-      </c>
-      <c r="N4" s="52"/>
+        <v>153</v>
+      </c>
+      <c r="N4" s="53"/>
       <c r="P4" s="55" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q4" s="54"/>
+        <v>154</v>
+      </c>
+      <c r="Q4" s="52"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>159</v>
-      </c>
-      <c r="T4" s="54"/>
+        <v>155</v>
+      </c>
+      <c r="T4" s="52"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>160</v>
-      </c>
-      <c r="W4" s="54"/>
+        <v>156</v>
+      </c>
+      <c r="W4" s="52"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>161</v>
-      </c>
-      <c r="Z4" s="54"/>
+        <v>157</v>
+      </c>
+      <c r="Z4" s="52"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>162</v>
-      </c>
-      <c r="AC4" s="54"/>
+        <v>158</v>
+      </c>
+      <c r="AC4" s="52"/>
       <c r="AE4" s="55" t="s">
-        <v>163</v>
-      </c>
-      <c r="AF4" s="54"/>
+        <v>159</v>
+      </c>
+      <c r="AF4" s="52"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>164</v>
-      </c>
-      <c r="AI4" s="54"/>
+        <v>160</v>
+      </c>
+      <c r="AI4" s="52"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>165</v>
-      </c>
-      <c r="AL4" s="54"/>
+        <v>161</v>
+      </c>
+      <c r="AL4" s="52"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>166</v>
-      </c>
-      <c r="AO4" s="54"/>
+        <v>162</v>
+      </c>
+      <c r="AO4" s="52"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>167</v>
-      </c>
-      <c r="AR4" s="54"/>
+        <v>163</v>
+      </c>
+      <c r="AR4" s="52"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B5" s="37">
         <v>1</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E5" s="37">
         <v>2</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H5" s="37">
         <v>3</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="K5" s="37">
         <v>4</v>
       </c>
       <c r="M5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="N5" s="37">
         <v>5</v>
       </c>
       <c r="P5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Q5" s="37">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="T5" s="37">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="W5" s="37">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Z5" s="37">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AC5" s="37">
         <v>10</v>
       </c>
       <c r="AE5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AF5" s="37">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AI5" s="37">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AL5" s="37">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AO5" s="37">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AR5" s="37">
         <v>15</v>
@@ -7862,172 +8543,172 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B7" s="37"/>
       <c r="D7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E7" s="37"/>
       <c r="G7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H7" s="37"/>
       <c r="J7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K7" s="37"/>
       <c r="M7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="N7" s="37"/>
       <c r="P7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="Q7" s="37"/>
       <c r="R7" s="1"/>
       <c r="S7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="T7" s="37"/>
       <c r="U7" s="1"/>
       <c r="V7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="W7" s="37"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="Z7" s="37"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AC7" s="37"/>
       <c r="AE7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AF7" s="37"/>
       <c r="AG7" s="1"/>
       <c r="AH7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AI7" s="37"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AL7" s="37"/>
       <c r="AM7" s="1"/>
       <c r="AN7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AO7" s="37"/>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AR7" s="37"/>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="U8" s="1"/>
       <c r="V8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AA8" s="1"/>
       <c r="AB8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AG8" s="1"/>
       <c r="AH8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AL8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AM8" s="1"/>
       <c r="AN8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AO8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AR8" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
@@ -8892,6 +9573,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="Y6:Z6"/>
     <mergeCell ref="AQ4:AR4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
@@ -8901,27 +9596,13 @@
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="S4:T4"/>
     <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AN6:AO6"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="AK4:AL4"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="V4:W4"/>
     <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="V6:W6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8955,277 +9636,277 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" s="53"/>
+      <c r="D4" s="55" t="s">
+        <v>171</v>
+      </c>
+      <c r="E4" s="53"/>
+      <c r="G4" s="55" t="s">
+        <v>172</v>
+      </c>
+      <c r="H4" s="53"/>
+      <c r="J4" s="55" t="s">
+        <v>173</v>
+      </c>
+      <c r="K4" s="53"/>
+      <c r="M4" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="B4" s="52"/>
-      <c r="D4" s="55" t="s">
+      <c r="N4" s="53"/>
+      <c r="P4" s="55" t="s">
         <v>175</v>
       </c>
-      <c r="E4" s="52"/>
-      <c r="G4" s="55" t="s">
-        <v>176</v>
-      </c>
-      <c r="H4" s="52"/>
-      <c r="J4" s="55" t="s">
-        <v>177</v>
-      </c>
-      <c r="K4" s="52"/>
-      <c r="M4" s="55" t="s">
-        <v>178</v>
-      </c>
-      <c r="N4" s="52"/>
-      <c r="P4" s="55" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q4" s="54"/>
+      <c r="Q4" s="52"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>180</v>
-      </c>
-      <c r="T4" s="54"/>
+        <v>176</v>
+      </c>
+      <c r="T4" s="52"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>181</v>
-      </c>
-      <c r="W4" s="54"/>
+        <v>177</v>
+      </c>
+      <c r="W4" s="52"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z4" s="54"/>
+        <v>178</v>
+      </c>
+      <c r="Z4" s="52"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>183</v>
-      </c>
-      <c r="AC4" s="54"/>
+        <v>179</v>
+      </c>
+      <c r="AC4" s="52"/>
       <c r="AE4" s="55" t="s">
-        <v>184</v>
-      </c>
-      <c r="AF4" s="54"/>
+        <v>180</v>
+      </c>
+      <c r="AF4" s="52"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>185</v>
-      </c>
-      <c r="AI4" s="54"/>
+        <v>181</v>
+      </c>
+      <c r="AI4" s="52"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>186</v>
-      </c>
-      <c r="AL4" s="54"/>
+        <v>182</v>
+      </c>
+      <c r="AL4" s="52"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>187</v>
-      </c>
-      <c r="AO4" s="54"/>
+        <v>183</v>
+      </c>
+      <c r="AO4" s="52"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>188</v>
-      </c>
-      <c r="AR4" s="54"/>
+        <v>184</v>
+      </c>
+      <c r="AR4" s="52"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="H5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="M5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="N5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="P5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="Q5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="T5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="W5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="Z5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AC5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AE5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AF5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AI5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AL5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AO5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AR5" s="39" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B6" s="39">
         <v>1</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E6" s="39">
         <v>2</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H6" s="39">
         <v>3</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="K6" s="39">
         <v>4</v>
       </c>
       <c r="M6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="N6" s="39">
         <v>5</v>
       </c>
       <c r="P6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Q6" s="39">
         <v>6</v>
       </c>
       <c r="R6" s="1"/>
       <c r="S6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="T6" s="39">
         <v>7</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="W6" s="39">
         <v>8</v>
       </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="Z6" s="39">
         <v>9</v>
       </c>
       <c r="AA6" s="1"/>
       <c r="AB6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AC6" s="39">
         <v>10</v>
       </c>
       <c r="AE6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AF6" s="39">
         <v>11</v>
       </c>
       <c r="AG6" s="1"/>
       <c r="AH6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AI6" s="39">
         <v>12</v>
       </c>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AL6" s="39">
         <v>13</v>
       </c>
       <c r="AM6" s="1"/>
       <c r="AN6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AO6" s="39">
         <v>14</v>
       </c>
       <c r="AP6" s="1"/>
       <c r="AQ6" s="38" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AR6" s="39">
         <v>15</v>
@@ -9318,172 +9999,172 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B8" s="39"/>
       <c r="D8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E8" s="39"/>
       <c r="G8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H8" s="39"/>
       <c r="J8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K8" s="39"/>
       <c r="M8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="N8" s="39"/>
       <c r="P8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="Q8" s="39"/>
       <c r="R8" s="1"/>
       <c r="S8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="T8" s="39"/>
       <c r="U8" s="1"/>
       <c r="V8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="W8" s="39"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="Z8" s="39"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AC8" s="39"/>
       <c r="AE8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AF8" s="39"/>
       <c r="AG8" s="1"/>
       <c r="AH8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AI8" s="39"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AL8" s="39"/>
       <c r="AM8" s="1"/>
       <c r="AN8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AO8" s="39"/>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AR8" s="39"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="U9" s="1"/>
       <c r="V9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AA9" s="1"/>
       <c r="AB9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AE9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AG9" s="1"/>
       <c r="AH9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AL9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AM9" s="1"/>
       <c r="AN9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AO9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AP9" s="1"/>
       <c r="AQ9" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="AR9" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
@@ -10288,35 +10969,35 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="AN7:AO7"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AQ7:AR7"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AH4:AI4"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="S7:T7"/>
     <mergeCell ref="M7:N7"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="Y7:Z7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="AQ4:AR4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="AB7:AC7"/>
+    <mergeCell ref="AQ7:AR7"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="Y7:Z7"/>
+    <mergeCell ref="AQ4:AR4"/>
     <mergeCell ref="Y4:Z4"/>
     <mergeCell ref="AE7:AF7"/>
     <mergeCell ref="AK7:AL7"/>
     <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="AB7:AC7"/>
+    <mergeCell ref="AN7:AO7"/>
     <mergeCell ref="AH7:AI7"/>
   </mergeCells>
   <conditionalFormatting sqref="B6 A7:B7">
@@ -10414,20 +11095,20 @@
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="59" t="s">
-        <v>191</v>
-      </c>
-      <c r="B2" s="54"/>
+        <v>187</v>
+      </c>
+      <c r="B2" s="52"/>
       <c r="D2" s="60" t="s">
-        <v>192</v>
-      </c>
-      <c r="E2" s="54"/>
+        <v>188</v>
+      </c>
+      <c r="E2" s="52"/>
       <c r="G2" s="22" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="32" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
@@ -10435,7 +11116,7 @@
         </is>
       </c>
       <c r="D3" s="34" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E3" s="35" t="inlineStr">
         <is>
@@ -10446,19 +11127,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -10471,7 +11152,7 @@
         <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -10480,10 +11161,10 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="G6" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -10620,31 +11301,31 @@
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E2" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="F2" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="J2" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>206</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>5</v>
@@ -10672,10 +11353,10 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="J3" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -10690,10 +11371,10 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="J4" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -10708,10 +11389,10 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="J5" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="K5" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -10738,7 +11419,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="J7" s="5" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -10753,7 +11434,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="J8" s="14" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="K8"/>
     </row>
@@ -10769,7 +11450,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="J9" s="14" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="K9"/>
     </row>
@@ -10785,7 +11466,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="J10" s="14" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="K10"/>
     </row>
@@ -10801,7 +11482,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="J11" s="14" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="K11"/>
     </row>
@@ -10817,31 +11498,31 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="J12" s="14" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="K12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J13" s="14" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="K13"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J14" s="14" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="K14"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J15" s="14" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="K15"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J16" s="14" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -10850,7 +11531,7 @@
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J17" s="14" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="K17"/>
     </row>
@@ -10891,16 +11572,16 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>5</v>
@@ -10911,10 +11592,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -10922,10 +11603,10 @@
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="E4" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F4" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -10933,10 +11614,10 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="E5" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -11066,122 +11747,122 @@
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="61" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="61" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="61" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="61" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="61" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="61" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
@@ -11566,18 +12247,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="B4:D4"/>
     <mergeCell ref="V5:W5"/>
+    <mergeCell ref="F4:H4"/>
     <mergeCell ref="V4:X4"/>
-    <mergeCell ref="R4:T4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:O5"/>
     <mergeCell ref="R5:S5"/>
-    <mergeCell ref="F5:G5"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5 H5 L5 P5 T5 X5" xr:uid="{00000000-0002-0000-0700-000000000000}">
@@ -11615,122 +12296,122 @@
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="63" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="63" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="63" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="63" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="63" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="63" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
@@ -12115,18 +12796,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="B4:D4"/>
     <mergeCell ref="V5:W5"/>
+    <mergeCell ref="F4:H4"/>
     <mergeCell ref="V4:X4"/>
-    <mergeCell ref="R4:T4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:O5"/>
     <mergeCell ref="R5:S5"/>
-    <mergeCell ref="F5:G5"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5 H5 L5 P5 T5 X5" xr:uid="{00000000-0002-0000-0800-000000000000}">

--- a/docs/seep/files/xslope_johnson_res.xlsx
+++ b/docs/seep/files/xslope_johnson_res.xlsx
@@ -6592,7 +6592,9 @@
       <c r="K11" s="3">
         <v>0.0</v>
       </c>
-      <c r="L11" s="3"/>
+      <c r="L11" s="3">
+        <v>0</v>
+      </c>
       <c r="M11" s="3">
         <v>2000000.0</v>
       </c>
@@ -6716,7 +6718,9 @@
       <c r="K12" s="3">
         <v>0.0</v>
       </c>
-      <c r="L12" s="3"/>
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
       <c r="M12" s="3">
         <v>200000.0</v>
       </c>
@@ -6840,7 +6844,9 @@
       <c r="K13" s="3">
         <v>0.0</v>
       </c>
-      <c r="L13" s="3"/>
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
       <c r="M13" s="3">
         <v>1000000.0</v>
       </c>

--- a/docs/seep/files/xslope_johnson_res.xlsx
+++ b/docs/seep/files/xslope_johnson_res.xlsx
@@ -6592,9 +6592,7 @@
       <c r="K11" s="3">
         <v>0.0</v>
       </c>
-      <c r="L11" s="3">
-        <v>0</v>
-      </c>
+      <c r="L11" s="3"/>
       <c r="M11" s="3">
         <v>2000000.0</v>
       </c>
@@ -6718,9 +6716,7 @@
       <c r="K12" s="3">
         <v>0.0</v>
       </c>
-      <c r="L12" s="3">
-        <v>0</v>
-      </c>
+      <c r="L12" s="3"/>
       <c r="M12" s="3">
         <v>200000.0</v>
       </c>
@@ -6844,9 +6840,7 @@
       <c r="K13" s="3">
         <v>0.0</v>
       </c>
-      <c r="L13" s="3">
-        <v>0</v>
-      </c>
+      <c r="L13" s="3"/>
       <c r="M13" s="3">
         <v>1000000.0</v>
       </c>

--- a/docs/seep/files/xslope_johnson_res.xlsx
+++ b/docs/seep/files/xslope_johnson_res.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC02AEA9-EA56-1649-9CD0-1ADB754CC06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12967D2-A998-D342-B5ED-43CABE326A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18260" yWindow="3440" windowWidth="44060" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15680" yWindow="4780" windowWidth="46940" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="319">
   <si>
     <t>XSLOPE Input Template</t>
   </si>
@@ -343,9 +343,6 @@
     <t>vg</t>
   </si>
   <si>
-    <t>van Genuchten model (a, n)</t>
-  </si>
-  <si>
     <t>pow</t>
   </si>
   <si>
@@ -875,9 +872,6 @@
   </si>
   <si>
     <t>I</t>
-  </si>
-  <si>
-    <t>Fixity</t>
   </si>
   <si>
     <t>P</t>
@@ -1113,6 +1107,36 @@
       </rPr>
       <t>sat</t>
     </r>
+  </si>
+  <si>
+    <t>yr</t>
+  </si>
+  <si>
+    <t>Adhesion</t>
+  </si>
+  <si>
+    <t>Delta</t>
+  </si>
+  <si>
+    <t>1D element size:</t>
+  </si>
+  <si>
+    <t>Head</t>
+  </si>
+  <si>
+    <t>Tip</t>
+  </si>
+  <si>
+    <t>Pinned</t>
+  </si>
+  <si>
+    <t>Unrotated</t>
+  </si>
+  <si>
+    <t>van Genuchten model (a, n, l)</t>
+  </si>
+  <si>
+    <t>l</t>
   </si>
 </sst>
 </file>
@@ -1574,16 +1598,16 @@
     <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1883,16 +1907,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>217714</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>54430</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>199571</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>9071</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>90714</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1907,8 +1931,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14804571" y="254001"/>
-          <a:ext cx="3610429" cy="3746499"/>
+          <a:off x="16455571" y="254001"/>
+          <a:ext cx="3855358" cy="4027713"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2032,6 +2056,31 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Adhesion</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = soii-reinforcement interface adhesion (blank</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+            <a:t> = use Lp)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>Delta</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+            <a:t> = soil-reinforcement interface friction angle (blank = use Lp)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
             <a:t>Tend1, Tend2 </a:t>
           </a:r>
           <a:r>
@@ -2078,6 +2127,10 @@
             <a:rPr lang="en-US" sz="1100" b="0"/>
             <a:t> = cross-sectional area of reinforcement (FEM only)</a:t>
           </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+          </a:br>
+          <a:endParaRPr lang="en-US" sz="1100" b="0"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2090,16 +2143,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>308429</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>290286</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>190499</xdr:rowOff>
+      <xdr:rowOff>126999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>571501</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>145143</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>553358</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2114,8 +2167,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13398500" y="190499"/>
-          <a:ext cx="3156858" cy="2349501"/>
+          <a:off x="14205857" y="126999"/>
+          <a:ext cx="3156858" cy="2521858"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2420,7 +2473,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Fixity</a:t>
+            <a:t>Head</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
@@ -2432,8 +2485,54 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> = Pile head status (fixed or free)</a:t>
+            <a:t> = Pile head fixity status</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Tip</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Pile tip fixity status</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
           <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
@@ -2760,7 +2859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.6640625" customWidth="1"/>
@@ -2785,15 +2884,15 @@
         <v>2</v>
       </c>
       <c r="D5" s="30">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
       <c r="F7" s="15" t="s">
         <v>4</v>
       </c>
@@ -2965,7 +3064,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C20" s="14" t="s">
-        <v>45</v>
+        <v>312</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>46</v>
@@ -2977,7 +3076,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C21" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>49</v>
@@ -2989,28 +3088,34 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C22" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="1"/>
+        <v>48</v>
+      </c>
       <c r="F22" s="1"/>
+      <c r="D22"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="1"/>
       <c r="C23" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24" s="1"/>
+      <c r="C24" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D24" s="1" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B24" s="1"/>
-      <c r="C24" s="14" t="s">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C25" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D24"/>
+      <c r="D25"/>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D49" s="1" t="s">
@@ -3052,93 +3157,98 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D59" s="1" t="s">
-        <v>62</v>
+    <row r="58" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D58" s="1" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="60" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D60" s="1" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D61" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D62" s="1" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="63" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D63" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="64" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D64" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D65" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D66" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D67" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D68" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D69" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D70" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D71" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D72" s="1" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="73" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D73" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="74" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D74" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="75" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D75" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="76" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D76" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D77" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D78" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D79" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3147,28 +3257,28 @@
     <mergeCell ref="B7:D7"/>
   </mergeCells>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D22" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"rollers,fixed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$D$50:$D$51</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>$D$54:$D$57</formula1>
+      <formula1>$D$54:$D$58</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D17" xr:uid="{00000000-0002-0000-0000-000003000000}">
-      <formula1>$D$60:$D$61</formula1>
+      <formula1>$D$61:$D$62</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D14" xr:uid="{00000000-0002-0000-0000-000004000000}">
-      <formula1>$D$64:$D$71</formula1>
+      <formula1>$D$65:$D$72</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D18" xr:uid="{00000000-0002-0000-0000-000005000000}">
-      <formula1>$D$74:$D$78</formula1>
+      <formula1>$D$75:$D$79</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D24" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"auto,manual"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D24" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D25" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"circular,non-circular"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3178,83 +3288,89 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A2:AB25"/>
+  <dimension ref="A2:AD25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="6" width="10.83203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.1640625" customWidth="1"/>
-    <col min="10" max="12" width="10.83203125" style="1" customWidth="1"/>
-    <col min="16" max="18" width="10.83203125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="4.33203125" customWidth="1"/>
+    <col min="10" max="14" width="10.83203125" style="1" customWidth="1"/>
+    <col min="18" max="20" width="10.83203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="40" t="s">
         <v>246</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="H2" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="I2" s="40" t="s">
         <v>248</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="J2" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="K2" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="L2" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="M2" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="N2" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="O2" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="P2" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="Q2" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="R2" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="S2" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="T2" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="Q2" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="R2" s="28" t="s">
+      <c r="AB2" t="s">
         <v>257</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AC2" t="s">
         <v>258</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AD2" t="s">
         <v>259</v>
       </c>
-      <c r="AB2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -3265,11 +3381,11 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="str">
-        <f t="shared" ref="H3:H22" si="0">IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,2,0),""))</f>
+        <f t="shared" ref="H3:H22" si="0">IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I3" s="3" t="str">
-        <f t="shared" ref="I3:I22" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,3,0),""))</f>
+        <f t="shared" ref="I3:I22" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J3" s="3"/>
@@ -3281,17 +3397,19 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
-      <c r="Z3" t="s">
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="AB3" t="s">
+        <v>260</v>
+      </c>
+      <c r="AC3" t="s">
         <v>261</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AD3" t="s">
         <v>262</v>
       </c>
-      <c r="AB3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -3318,11 +3436,13 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
-      <c r="Z4" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="AB4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -3349,11 +3469,13 @@
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
-      <c r="Z5" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="AB5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -3380,8 +3502,10 @@
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -3408,8 +3532,10 @@
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -3436,17 +3562,19 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
-      <c r="Z8" t="s">
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="AB8" t="s">
+        <v>257</v>
+      </c>
+      <c r="AC8" t="s">
         <v>258</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AD8" t="s">
         <v>259</v>
       </c>
-      <c r="AB8" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -3473,17 +3601,19 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
-      <c r="Z9" t="s">
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="AB9" t="s">
+        <v>260</v>
+      </c>
+      <c r="AC9" t="s">
         <v>261</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="AD9" t="s">
         <v>262</v>
       </c>
-      <c r="AB9" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -3510,17 +3640,19 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
-      <c r="Z10" t="s">
-        <v>264</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>262</v>
-      </c>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
       <c r="AB10" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+        <v>263</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>261</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -3547,17 +3679,19 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-      <c r="Z11" t="s">
-        <v>265</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>262</v>
-      </c>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
       <c r="AB11" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+        <v>264</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>261</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -3584,8 +3718,10 @@
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -3612,8 +3748,10 @@
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -3640,8 +3778,10 @@
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -3668,8 +3808,10 @@
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -3696,8 +3838,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -3724,8 +3868,10 @@
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -3752,8 +3898,10 @@
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -3780,8 +3928,10 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -3808,8 +3958,10 @@
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -3836,8 +3988,10 @@
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -3864,39 +4018,41 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="T23" s="42"/>
-      <c r="U23" t="s">
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="V23" s="42"/>
+      <c r="W23" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="26"/>
+      <c r="W24" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
-      <c r="T25" s="29"/>
-      <c r="U25" s="9" t="s">
-        <v>104</v>
+      <c r="V25" s="29"/>
+      <c r="W25" s="9" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G22" xr:uid="{00000000-0002-0000-0900-000000000000}">
-      <formula1>$Z$2:$Z$5</formula1>
+      <formula1>$AB$2:$AB$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H22" xr:uid="{00000000-0002-0000-0900-000001000000}">
-      <formula1>$AA$2:$AA$3</formula1>
+      <formula1>$AC$2:$AC$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I22" xr:uid="{00000000-0002-0000-0900-000002000000}">
-      <formula1>$AB$2:$AB$3</formula1>
+      <formula1>$AD$2:$AD$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3906,74 +4062,77 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A2:Z17"/>
+  <dimension ref="A2:AA17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="1" customWidth="1"/>
     <col min="3" max="7" width="10.83203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="14.5" customWidth="1"/>
-    <col min="9" max="16" width="10.83203125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="5.5" customWidth="1"/>
+    <col min="9" max="17" width="10.83203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>246</v>
-      </c>
       <c r="G2" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>248</v>
+      </c>
+      <c r="I2" s="27" t="s">
         <v>266</v>
       </c>
-      <c r="H2" s="40" t="s">
-        <v>249</v>
-      </c>
-      <c r="I2" s="27" t="s">
+      <c r="J2" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="K2" s="41" t="s">
         <v>268</v>
       </c>
-      <c r="K2" s="41" t="s">
+      <c r="L2" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="L2" s="41" t="s">
+      <c r="M2" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="N2" s="28" t="s">
         <v>270</v>
       </c>
-      <c r="M2" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="N2" s="28" t="s">
-        <v>271</v>
-      </c>
       <c r="O2" s="28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P2" s="28" t="s">
-        <v>272</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>222</v>
+        <v>313</v>
+      </c>
+      <c r="Q2" s="28" t="s">
+        <v>314</v>
       </c>
       <c r="Z2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+        <v>221</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -3992,14 +4151,15 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
-      <c r="Y3" t="s">
-        <v>226</v>
-      </c>
+      <c r="Q3" s="3"/>
       <c r="Z3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -4018,8 +4178,12 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q4" s="3"/>
+      <c r="Z4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -4038,8 +4202,12 @@
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q5" s="3"/>
+      <c r="Z5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -4058,8 +4226,9 @@
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q6" s="3"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -4078,8 +4247,9 @@
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q7" s="3"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -4098,8 +4268,9 @@
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -4118,8 +4289,9 @@
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -4138,8 +4310,9 @@
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -4158,8 +4331,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -4178,36 +4352,37 @@
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="R15" s="42"/>
-      <c r="S15" t="s">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="S15" s="42"/>
+      <c r="T15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="R16" s="26"/>
-      <c r="S16" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="18:19" x14ac:dyDescent="0.2">
-      <c r="R17" s="29"/>
-      <c r="S17" s="9" t="s">
-        <v>104</v>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="S16" s="26"/>
+      <c r="T16" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="19:20" x14ac:dyDescent="0.2">
+      <c r="S17" s="29"/>
+      <c r="T17" s="9" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:P12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
-      <formula1>$Y$2:$Y$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
+      <formula1>$AA$2:$AA$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
-      <formula1>$Z$2:$Z$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:Q12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+      <formula1>$Z$2:$Z$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4227,22 +4402,22 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>167</v>
-      </c>
       <c r="E2" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -4465,29 +4640,29 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="64" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="59" t="s">
+        <v>274</v>
+      </c>
+      <c r="F2" s="54"/>
+      <c r="H2" s="59" t="s">
+        <v>275</v>
+      </c>
+      <c r="I2" s="54"/>
+      <c r="K2" s="59" t="s">
         <v>276</v>
       </c>
-      <c r="F2" s="52"/>
-      <c r="H2" s="59" t="s">
+      <c r="L2" s="54"/>
+      <c r="N2" s="59" t="s">
         <v>277</v>
       </c>
-      <c r="I2" s="52"/>
-      <c r="K2" s="59" t="s">
+      <c r="O2" s="54"/>
+      <c r="Q2" s="59" t="s">
         <v>278</v>
       </c>
-      <c r="L2" s="52"/>
-      <c r="N2" s="59" t="s">
-        <v>279</v>
-      </c>
-      <c r="O2" s="52"/>
-      <c r="Q2" s="59" t="s">
-        <v>280</v>
-      </c>
-      <c r="R2" s="52"/>
+      <c r="R2" s="54"/>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B3" s="66"/>
@@ -4509,63 +4684,63 @@
         <v>100.0</v>
       </c>
       <c r="K3" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L3" s="33"/>
       <c r="N3" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="O3" s="33"/>
       <c r="Q3" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="R3" s="33"/>
       <c r="T3" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="E4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="H4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="I4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="K4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="L4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="L4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="N4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="O4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="O4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="Q4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="R4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="T4" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="U4" t="s">
         <v>281</v>
-      </c>
-      <c r="U4" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -4594,10 +4769,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="U5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -4626,7 +4801,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="T6" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="U6" s="9"/>
     </row>
@@ -4919,99 +5094,99 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="68" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="60" t="s">
+        <v>286</v>
+      </c>
+      <c r="F2" s="54"/>
+      <c r="H2" s="60" t="s">
+        <v>287</v>
+      </c>
+      <c r="I2" s="54"/>
+      <c r="K2" s="60" t="s">
         <v>288</v>
       </c>
-      <c r="F2" s="52"/>
-      <c r="H2" s="60" t="s">
+      <c r="L2" s="54"/>
+      <c r="N2" s="60" t="s">
         <v>289</v>
       </c>
-      <c r="I2" s="52"/>
-      <c r="K2" s="60" t="s">
+      <c r="O2" s="54"/>
+      <c r="Q2" s="60" t="s">
         <v>290</v>
       </c>
-      <c r="L2" s="52"/>
-      <c r="N2" s="60" t="s">
-        <v>291</v>
-      </c>
-      <c r="O2" s="52"/>
-      <c r="Q2" s="60" t="s">
-        <v>292</v>
-      </c>
-      <c r="R2" s="52"/>
+      <c r="R2" s="54"/>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B3" s="66"/>
       <c r="C3" s="67"/>
       <c r="E3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F3" s="35"/>
       <c r="H3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I3" s="35"/>
       <c r="K3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L3" s="35"/>
       <c r="N3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="O3" s="35"/>
       <c r="Q3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="R3" s="35"/>
       <c r="T3" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="E4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="H4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="I4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="K4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="L4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="L4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="N4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="O4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="O4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="Q4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="R4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="T4" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="U4" t="s">
         <v>281</v>
-      </c>
-      <c r="U4" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -5028,10 +5203,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="U5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -5330,22 +5505,22 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B2" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="D2" s="50" t="s">
         <v>293</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="E2" s="50" t="s">
         <v>294</v>
       </c>
-      <c r="D2" s="50" t="s">
+      <c r="F2" s="50" t="s">
         <v>295</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="G2" s="50" t="s">
         <v>296</v>
-      </c>
-      <c r="F2" s="50" t="s">
-        <v>297</v>
-      </c>
-      <c r="G2" s="50" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
@@ -5356,7 +5531,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="I3" s="14" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -5378,7 +5553,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="I5" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -5400,7 +5575,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="I7" s="14" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -5412,7 +5587,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="I8" s="14" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -5424,7 +5599,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="14" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -5444,7 +5619,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="J11" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
@@ -6255,16 +6430,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:AP52"/>
+  <dimension ref="A2:AQ52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" style="1" customWidth="1"/>
     <col min="3" max="10" width="8.5" style="1" customWidth="1"/>
-    <col min="11" max="41" width="8.5" customWidth="1"/>
+    <col min="11" max="42" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C2" s="6" t="s">
         <v>79</v>
       </c>
@@ -6279,7 +6454,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C3" s="1" t="s">
         <v>83</v>
       </c>
@@ -6300,7 +6475,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
         <v>89</v>
       </c>
@@ -6322,241 +6497,245 @@
         <v>93</v>
       </c>
       <c r="AK4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="C5" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="C5" s="1" t="s">
+      <c r="D5" t="s">
         <v>95</v>
-      </c>
-      <c r="D5" t="s">
-        <v>96</v>
       </c>
       <c r="L5" s="26"/>
       <c r="M5" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="AD5" s="14"/>
       <c r="AJ5" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AK5" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="AK5" s="9" t="s">
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="C6" s="1" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="9" t="s">
         <v>102</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>103</v>
       </c>
       <c r="L6" s="29"/>
       <c r="M6" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="P6" t="s">
         <v>105</v>
-      </c>
-      <c r="P6" t="s">
-        <v>106</v>
       </c>
       <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>107</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>108</v>
       </c>
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="C9" s="51" t="s">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="C9" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="54"/>
+      <c r="M9" s="54"/>
+      <c r="N9" s="54"/>
+      <c r="O9" s="54"/>
+      <c r="P9" s="54"/>
+      <c r="Q9" s="54"/>
+      <c r="R9" s="54"/>
+      <c r="S9" s="54"/>
+      <c r="T9" s="54"/>
+      <c r="U9" s="54"/>
+      <c r="V9" s="54"/>
+      <c r="W9" s="54"/>
+      <c r="X9" s="54"/>
+      <c r="Y9" s="54"/>
+      <c r="Z9" s="54"/>
+      <c r="AA9" s="53" t="s">
         <v>109</v>
       </c>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="52"/>
-      <c r="L9" s="52"/>
-      <c r="M9" s="52"/>
-      <c r="N9" s="52"/>
-      <c r="O9" s="52"/>
-      <c r="P9" s="52"/>
-      <c r="Q9" s="52"/>
-      <c r="R9" s="52"/>
-      <c r="S9" s="52"/>
-      <c r="T9" s="52"/>
-      <c r="U9" s="52"/>
-      <c r="V9" s="52"/>
-      <c r="W9" s="52"/>
-      <c r="X9" s="52"/>
-      <c r="Y9" s="52"/>
-      <c r="Z9" s="52"/>
-      <c r="AA9" s="51" t="s">
+      <c r="AB9" s="54"/>
+      <c r="AC9" s="54"/>
+      <c r="AD9" s="54"/>
+      <c r="AE9" s="54"/>
+      <c r="AF9" s="54"/>
+      <c r="AG9" s="53" t="s">
         <v>110</v>
       </c>
-      <c r="AB9" s="52"/>
-      <c r="AC9" s="52"/>
-      <c r="AD9" s="52"/>
-      <c r="AE9" s="52"/>
-      <c r="AF9" s="52"/>
-      <c r="AG9" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="AH9" s="52"/>
-      <c r="AI9" s="52"/>
-      <c r="AJ9" s="52"/>
-      <c r="AK9" s="52"/>
-      <c r="AL9" s="52"/>
-      <c r="AM9" s="52"/>
-      <c r="AN9" s="52"/>
-      <c r="AO9" s="52"/>
-      <c r="AP9" s="52"/>
-    </row>
-    <row r="10" spans="1:42" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AH9" s="54"/>
+      <c r="AI9" s="54"/>
+      <c r="AJ9" s="54"/>
+      <c r="AK9" s="54"/>
+      <c r="AL9" s="54"/>
+      <c r="AM9" s="54"/>
+      <c r="AN9" s="54"/>
+      <c r="AO9" s="54"/>
+      <c r="AP9" s="54"/>
+      <c r="AQ9" s="54"/>
+    </row>
+    <row r="10" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="D10" s="48" t="s">
+        <v>308</v>
+      </c>
+      <c r="E10" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="48" t="s">
-        <v>310</v>
-      </c>
-      <c r="E10" s="44" t="s">
+      <c r="F10" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="G10" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="G10" s="45" t="s">
+      <c r="H10" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="I10" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="I10" s="44" t="s">
+      <c r="J10" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="J10" s="49" t="s">
+      <c r="K10" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="K10" s="49" t="s">
+      <c r="L10" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="L10" s="21" t="s">
+      <c r="M10" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="M10" s="21" t="s">
+      <c r="N10" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="N10" s="43" t="s">
+      <c r="O10" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="O10" s="44" t="s">
+      <c r="P10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q10" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="P10" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q10" s="44" t="s">
+      <c r="R10" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="R10" s="44" t="s">
+      <c r="S10" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="S10" s="44" t="s">
+      <c r="T10" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="T10" s="44" t="s">
+      <c r="U10" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="U10" s="44" t="s">
+      <c r="V10" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="V10" s="44" t="s">
+      <c r="W10" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="W10" s="44" t="s">
+      <c r="X10" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="X10" s="44" t="s">
+      <c r="Y10" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="Y10" s="44" t="s">
+      <c r="Z10" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="Z10" s="44" t="s">
+      <c r="AA10" s="46" t="s">
+        <v>304</v>
+      </c>
+      <c r="AB10" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC10" s="47" t="s">
         <v>134</v>
       </c>
-      <c r="AA10" s="46" t="s">
+      <c r="AD10" s="46" t="s">
+        <v>305</v>
+      </c>
+      <c r="AE10" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="AB10" s="46" t="s">
-        <v>305</v>
-      </c>
-      <c r="AC10" s="47" t="s">
+      <c r="AF10" s="47" t="s">
+        <v>307</v>
+      </c>
+      <c r="AG10" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="AD10" s="46" t="s">
-        <v>307</v>
-      </c>
-      <c r="AE10" s="46" t="s">
-        <v>308</v>
-      </c>
-      <c r="AF10" s="47" t="s">
-        <v>309</v>
-      </c>
-      <c r="AG10" s="23" t="s">
+      <c r="AH10" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="AH10" s="23" t="s">
+      <c r="AI10" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="AI10" s="23" t="s">
+      <c r="AJ10" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="AJ10" s="23" t="s">
+      <c r="AK10" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="AK10" s="23" t="s">
+      <c r="AL10" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="AL10" s="23" t="s">
+      <c r="AM10" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="AM10" s="23" t="s">
+      <c r="AN10" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="AN10" s="23" t="s">
+      <c r="AO10" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="AP10" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="AO10" s="23" t="s">
+      <c r="AQ10" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="AP10" s="23" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>1</v>
       </c>
@@ -6593,7 +6772,7 @@
         <v>0.0</v>
       </c>
       <c r="L11" s="3">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M11" s="3">
         <v>2000000.0</v>
@@ -6679,10 +6858,13 @@
       <c r="AN11" s="3">
         <v>0.0</v>
       </c>
-      <c r="AO11" s="3"/>
+      <c r="AO11" s="3">
+        <v>0.5</v>
+      </c>
       <c r="AP11" s="3"/>
-    </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ11" s="3"/>
+    </row>
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -6719,7 +6901,7 @@
         <v>0.0</v>
       </c>
       <c r="L12" s="3">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M12" s="3">
         <v>200000.0</v>
@@ -6805,10 +6987,13 @@
       <c r="AN12" s="19">
         <v>0.0</v>
       </c>
-      <c r="AO12" s="19"/>
+      <c r="AO12" s="19">
+        <v>0.5</v>
+      </c>
       <c r="AP12" s="19"/>
-    </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ12" s="19"/>
+    </row>
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>3</v>
       </c>
@@ -6845,7 +7030,7 @@
         <v>0.0</v>
       </c>
       <c r="L13" s="3">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M13" s="3">
         <v>1000000.0</v>
@@ -6931,10 +7116,13 @@
       <c r="AN13" s="19">
         <v>0.0</v>
       </c>
-      <c r="AO13" s="19"/>
+      <c r="AO13" s="19">
+        <v>0.5</v>
+      </c>
       <c r="AP13" s="19"/>
-    </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ13" s="19"/>
+    </row>
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>4</v>
       </c>
@@ -6979,8 +7167,9 @@
       <c r="AN14" s="3"/>
       <c r="AO14" s="3"/>
       <c r="AP14" s="3"/>
-    </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ14" s="3"/>
+    </row>
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>5</v>
       </c>
@@ -7025,8 +7214,9 @@
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
-    </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ15" s="3"/>
+    </row>
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>6</v>
       </c>
@@ -7071,8 +7261,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
-    </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ16" s="3"/>
+    </row>
+    <row r="17" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>7</v>
       </c>
@@ -7117,8 +7308,9 @@
       <c r="AN17" s="3"/>
       <c r="AO17" s="3"/>
       <c r="AP17" s="3"/>
-    </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ17" s="3"/>
+    </row>
+    <row r="18" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>8</v>
       </c>
@@ -7163,8 +7355,9 @@
       <c r="AN18" s="3"/>
       <c r="AO18" s="3"/>
       <c r="AP18" s="3"/>
-    </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ18" s="3"/>
+    </row>
+    <row r="19" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>9</v>
       </c>
@@ -7209,8 +7402,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
-    </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ19" s="3"/>
+    </row>
+    <row r="20" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>10</v>
       </c>
@@ -7255,8 +7449,9 @@
       <c r="AN20" s="3"/>
       <c r="AO20" s="3"/>
       <c r="AP20" s="3"/>
-    </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ20" s="3"/>
+    </row>
+    <row r="21" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>11</v>
       </c>
@@ -7301,8 +7496,9 @@
       <c r="AN21" s="3"/>
       <c r="AO21" s="3"/>
       <c r="AP21" s="3"/>
-    </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ21" s="3"/>
+    </row>
+    <row r="22" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>12</v>
       </c>
@@ -7347,8 +7543,9 @@
       <c r="AN22" s="3"/>
       <c r="AO22" s="3"/>
       <c r="AP22" s="3"/>
-    </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ22" s="3"/>
+    </row>
+    <row r="23" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>13</v>
       </c>
@@ -7393,8 +7590,9 @@
       <c r="AN23" s="3"/>
       <c r="AO23" s="3"/>
       <c r="AP23" s="3"/>
-    </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ23" s="3"/>
+    </row>
+    <row r="24" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>14</v>
       </c>
@@ -7439,8 +7637,9 @@
       <c r="AN24" s="3"/>
       <c r="AO24" s="3"/>
       <c r="AP24" s="3"/>
-    </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ24" s="3"/>
+    </row>
+    <row r="25" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>15</v>
       </c>
@@ -7485,8 +7684,9 @@
       <c r="AN25" s="3"/>
       <c r="AO25" s="3"/>
       <c r="AP25" s="3"/>
-    </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ25" s="3"/>
+    </row>
+    <row r="26" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -7519,8 +7719,9 @@
       <c r="AN26" s="1"/>
       <c r="AO26" s="1"/>
       <c r="AP26" s="1"/>
-    </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ26" s="1"/>
+    </row>
+    <row r="27" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -7544,7 +7745,7 @@
       <c r="AE27" s="1"/>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -7568,7 +7769,7 @@
       <c r="AE28" s="1"/>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -7592,7 +7793,7 @@
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -7616,7 +7817,7 @@
       <c r="AE30" s="1"/>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -7640,7 +7841,7 @@
       <c r="AE31" s="1"/>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -8146,7 +8347,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="AG9:AP9"/>
+    <mergeCell ref="AG9:AQ9"/>
     <mergeCell ref="AA9:AF9"/>
     <mergeCell ref="C9:Z9"/>
   </mergeCells>
@@ -8226,7 +8427,7 @@
       <formula>OR($AJ11="vg",$AJ11="gard")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM11:AN52">
+  <conditionalFormatting sqref="AM11:AO52">
     <cfRule type="expression" dxfId="18" priority="1">
       <formula>$AJ11="lf"</formula>
     </cfRule>
@@ -8274,16 +8475,16 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B2" s="3">
         <v>0.0</v>
       </c>
       <c r="D2" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="N2" s="24" t="s">
         <v>147</v>
-      </c>
-      <c r="N2" s="24" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
@@ -8292,171 +8493,171 @@
           <t>Profile Line #1</t>
         </is>
       </c>
-      <c r="B4" s="53"/>
+      <c r="B4" s="52"/>
       <c r="D4" s="55" t="inlineStr">
         <is>
           <t>Profile Line #2</t>
         </is>
       </c>
-      <c r="E4" s="53"/>
+      <c r="E4" s="52"/>
       <c r="G4" s="55" t="inlineStr">
         <is>
           <t>Profile Line #3</t>
         </is>
       </c>
-      <c r="H4" s="53"/>
+      <c r="H4" s="52"/>
       <c r="J4" s="55" t="s">
+        <v>151</v>
+      </c>
+      <c r="K4" s="52"/>
+      <c r="M4" s="55" t="s">
         <v>152</v>
       </c>
-      <c r="K4" s="53"/>
-      <c r="M4" s="55" t="s">
+      <c r="N4" s="52"/>
+      <c r="P4" s="55" t="s">
         <v>153</v>
       </c>
-      <c r="N4" s="53"/>
-      <c r="P4" s="55" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q4" s="52"/>
+      <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>155</v>
-      </c>
-      <c r="T4" s="52"/>
+        <v>154</v>
+      </c>
+      <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>156</v>
-      </c>
-      <c r="W4" s="52"/>
+        <v>155</v>
+      </c>
+      <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>157</v>
-      </c>
-      <c r="Z4" s="52"/>
+        <v>156</v>
+      </c>
+      <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
+        <v>157</v>
+      </c>
+      <c r="AC4" s="54"/>
+      <c r="AE4" s="55" t="s">
         <v>158</v>
       </c>
-      <c r="AC4" s="52"/>
-      <c r="AE4" s="55" t="s">
-        <v>159</v>
-      </c>
-      <c r="AF4" s="52"/>
+      <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>160</v>
-      </c>
-      <c r="AI4" s="52"/>
+        <v>159</v>
+      </c>
+      <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>161</v>
-      </c>
-      <c r="AL4" s="52"/>
+        <v>160</v>
+      </c>
+      <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>162</v>
-      </c>
-      <c r="AO4" s="52"/>
+        <v>161</v>
+      </c>
+      <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>163</v>
-      </c>
-      <c r="AR4" s="52"/>
+        <v>162</v>
+      </c>
+      <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B5" s="37">
         <v>1</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E5" s="37">
         <v>2</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H5" s="37">
         <v>3</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K5" s="37">
         <v>4</v>
       </c>
       <c r="M5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N5" s="37">
         <v>5</v>
       </c>
       <c r="P5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q5" s="37">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="T5" s="37">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="W5" s="37">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Z5" s="37">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AC5" s="37">
         <v>10</v>
       </c>
       <c r="AE5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AF5" s="37">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AI5" s="37">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL5" s="37">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AO5" s="37">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AR5" s="37">
         <v>15</v>
@@ -8465,17 +8666,17 @@
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="56" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v/>
+        <v>shell</v>
       </c>
       <c r="B6" s="57"/>
       <c r="D6" s="56" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v/>
+        <v>core</v>
       </c>
       <c r="E6" s="57"/>
       <c r="G6" s="56" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v/>
+        <v>foundation</v>
       </c>
       <c r="H6" s="57"/>
       <c r="J6" s="56" t="str">
@@ -8549,172 +8750,172 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B7" s="37"/>
       <c r="D7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E7" s="37"/>
       <c r="G7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H7" s="37"/>
       <c r="J7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K7" s="37"/>
       <c r="M7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N7" s="37"/>
       <c r="P7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q7" s="37"/>
       <c r="R7" s="1"/>
       <c r="S7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T7" s="37"/>
       <c r="U7" s="1"/>
       <c r="V7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W7" s="37"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Z7" s="37"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AC7" s="37"/>
       <c r="AE7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AF7" s="37"/>
       <c r="AG7" s="1"/>
       <c r="AH7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI7" s="37"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AL7" s="37"/>
       <c r="AM7" s="1"/>
       <c r="AN7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AO7" s="37"/>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AR7" s="37"/>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="G8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="J8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="M8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="P8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="T8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="U8" s="1"/>
       <c r="V8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="W8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AA8" s="1"/>
       <c r="AB8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AC8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="AC8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="AE8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AF8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AF8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AG8" s="1"/>
       <c r="AH8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AI8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AL8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AM8" s="1"/>
       <c r="AN8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AO8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AO8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AR8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AR8" s="2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
@@ -9642,277 +9843,277 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>168</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" s="52"/>
+      <c r="D4" s="55" t="s">
         <v>170</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="D4" s="55" t="s">
+      <c r="E4" s="52"/>
+      <c r="G4" s="55" t="s">
         <v>171</v>
       </c>
-      <c r="E4" s="53"/>
-      <c r="G4" s="55" t="s">
+      <c r="H4" s="52"/>
+      <c r="J4" s="55" t="s">
         <v>172</v>
       </c>
-      <c r="H4" s="53"/>
-      <c r="J4" s="55" t="s">
+      <c r="K4" s="52"/>
+      <c r="M4" s="55" t="s">
         <v>173</v>
       </c>
-      <c r="K4" s="53"/>
-      <c r="M4" s="55" t="s">
+      <c r="N4" s="52"/>
+      <c r="P4" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="N4" s="53"/>
-      <c r="P4" s="55" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q4" s="52"/>
+      <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>176</v>
-      </c>
-      <c r="T4" s="52"/>
+        <v>175</v>
+      </c>
+      <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>177</v>
-      </c>
-      <c r="W4" s="52"/>
+        <v>176</v>
+      </c>
+      <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z4" s="52"/>
+        <v>177</v>
+      </c>
+      <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
+        <v>178</v>
+      </c>
+      <c r="AC4" s="54"/>
+      <c r="AE4" s="55" t="s">
         <v>179</v>
       </c>
-      <c r="AC4" s="52"/>
-      <c r="AE4" s="55" t="s">
-        <v>180</v>
-      </c>
-      <c r="AF4" s="52"/>
+      <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>181</v>
-      </c>
-      <c r="AI4" s="52"/>
+        <v>180</v>
+      </c>
+      <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>182</v>
-      </c>
-      <c r="AL4" s="52"/>
+        <v>181</v>
+      </c>
+      <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>183</v>
-      </c>
-      <c r="AO4" s="52"/>
+        <v>182</v>
+      </c>
+      <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>184</v>
-      </c>
-      <c r="AR4" s="52"/>
+        <v>183</v>
+      </c>
+      <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="B5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="B5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="D5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="E5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="E5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="G5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="H5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="H5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="J5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="K5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="K5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="M5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="N5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="N5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="P5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="Q5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="T5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="T5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="W5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="W5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="Z5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AC5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="AC5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="AE5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AF5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AF5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AI5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AI5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AL5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AL5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AO5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AO5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AR5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AR5" s="39" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B6" s="39">
         <v>1</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E6" s="39">
         <v>2</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H6" s="39">
         <v>3</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K6" s="39">
         <v>4</v>
       </c>
       <c r="M6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N6" s="39">
         <v>5</v>
       </c>
       <c r="P6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q6" s="39">
         <v>6</v>
       </c>
       <c r="R6" s="1"/>
       <c r="S6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="T6" s="39">
         <v>7</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="W6" s="39">
         <v>8</v>
       </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Z6" s="39">
         <v>9</v>
       </c>
       <c r="AA6" s="1"/>
       <c r="AB6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AC6" s="39">
         <v>10</v>
       </c>
       <c r="AE6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AF6" s="39">
         <v>11</v>
       </c>
       <c r="AG6" s="1"/>
       <c r="AH6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AI6" s="39">
         <v>12</v>
       </c>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL6" s="39">
         <v>13</v>
       </c>
       <c r="AM6" s="1"/>
       <c r="AN6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AO6" s="39">
         <v>14</v>
       </c>
       <c r="AP6" s="1"/>
       <c r="AQ6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AR6" s="39">
         <v>15</v>
@@ -9921,17 +10122,17 @@
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="58" t="str">
         <f>IF(OR(B5="",B5="material"),_xlfn.XLOOKUP(B6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
-        <v/>
+        <v>shell</v>
       </c>
       <c r="B7" s="57"/>
       <c r="D7" s="58" t="str">
         <f>IF(OR(E5="",E5="material"),_xlfn.XLOOKUP(E6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
-        <v/>
+        <v>core</v>
       </c>
       <c r="E7" s="57"/>
       <c r="G7" s="58" t="str">
         <f>IF(OR(H5="",H5="material"),_xlfn.XLOOKUP(H6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
-        <v/>
+        <v>foundation</v>
       </c>
       <c r="H7" s="57"/>
       <c r="J7" s="58" t="str">
@@ -10005,172 +10206,172 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B8" s="39"/>
       <c r="D8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E8" s="39"/>
       <c r="G8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H8" s="39"/>
       <c r="J8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K8" s="39"/>
       <c r="M8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N8" s="39"/>
       <c r="P8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q8" s="39"/>
       <c r="R8" s="1"/>
       <c r="S8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T8" s="39"/>
       <c r="U8" s="1"/>
       <c r="V8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W8" s="39"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Z8" s="39"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AC8" s="39"/>
       <c r="AE8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AF8" s="39"/>
       <c r="AG8" s="1"/>
       <c r="AH8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI8" s="39"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AL8" s="39"/>
       <c r="AM8" s="1"/>
       <c r="AN8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AO8" s="39"/>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AR8" s="39"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="G9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="J9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="M9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="N9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="P9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="T9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="U9" s="1"/>
       <c r="V9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="W9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Z9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AA9" s="1"/>
       <c r="AB9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AC9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="AC9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="AE9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AF9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AF9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AG9" s="1"/>
       <c r="AH9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AI9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AL9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AM9" s="1"/>
       <c r="AN9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AO9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AO9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AP9" s="1"/>
       <c r="AQ9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AR9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AR9" s="2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
@@ -10975,10 +11176,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="M7:N7"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="P4:Q4"/>
@@ -10987,12 +11184,13 @@
     <mergeCell ref="J7:K7"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="V7:W7"/>
     <mergeCell ref="P7:Q7"/>
     <mergeCell ref="AB7:AC7"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="S4:T4"/>
     <mergeCell ref="AQ7:AR7"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AH4:AI4"/>
@@ -11005,6 +11203,9 @@
     <mergeCell ref="AK4:AL4"/>
     <mergeCell ref="AN7:AO7"/>
     <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="V7:W7"/>
   </mergeCells>
   <conditionalFormatting sqref="B6 A7:B7">
     <cfRule type="expression" dxfId="17" priority="1">
@@ -11101,20 +11302,20 @@
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="59" t="s">
+        <v>186</v>
+      </c>
+      <c r="B2" s="54"/>
+      <c r="D2" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="D2" s="60" t="s">
+      <c r="E2" s="54"/>
+      <c r="G2" s="22" t="s">
         <v>188</v>
-      </c>
-      <c r="E2" s="52"/>
-      <c r="G2" s="22" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
@@ -11122,7 +11323,7 @@
         </is>
       </c>
       <c r="D3" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E3" s="35" t="inlineStr">
         <is>
@@ -11133,19 +11334,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D4" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="G4" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -11158,7 +11359,7 @@
         <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -11167,10 +11368,10 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="G6" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H6" t="s">
         <v>192</v>
-      </c>
-      <c r="H6" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -11307,31 +11508,31 @@
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="C2" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="D2" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="E2" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="F2" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="J2" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>5</v>
@@ -11359,10 +11560,10 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="J3" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -11377,10 +11578,10 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="J4" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>204</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -11395,10 +11596,10 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="J5" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K5" t="s">
         <v>206</v>
-      </c>
-      <c r="K5" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -11425,7 +11626,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="J7" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -11440,7 +11641,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="J8" s="14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K8"/>
     </row>
@@ -11456,7 +11657,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="J9" s="14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K9"/>
     </row>
@@ -11472,7 +11673,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="J10" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K10"/>
     </row>
@@ -11488,7 +11689,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="J11" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K11"/>
     </row>
@@ -11504,31 +11705,31 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="J12" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J13" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K13"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J14" s="14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K14"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J15" s="14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K15"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J16" s="14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -11537,7 +11738,7 @@
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J17" s="14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K17"/>
     </row>
@@ -11578,16 +11779,16 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>221</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>5</v>
@@ -11598,10 +11799,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F3" t="s">
         <v>222</v>
-      </c>
-      <c r="F3" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -11609,10 +11810,10 @@
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="E4" t="s">
+        <v>223</v>
+      </c>
+      <c r="F4" t="s">
         <v>224</v>
-      </c>
-      <c r="F4" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -11620,10 +11821,10 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="E5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F5" t="s">
         <v>226</v>
-      </c>
-      <c r="F5" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -11747,128 +11948,128 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" t="str">
-        <f>IF(main!$D$23="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
+        <f>IF(main!$D$24="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
         <v>Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.</v>
       </c>
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="61" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="61" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="61" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="61" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="61" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="61" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="L6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="P6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="T6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="X6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
@@ -12296,128 +12497,128 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" t="str">
-        <f>IF(main!$D$23="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
+        <f>IF(main!$D$24="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
         <v>Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.</v>
       </c>
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="63" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="63" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="63" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="63" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="63" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="63" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="L6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="P6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="T6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="X6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
